--- a/Spanish La Liga/X_pred.xlsx
+++ b/Spanish La Liga/X_pred.xlsx
@@ -1547,37 +1547,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
@@ -1592,13 +1592,13 @@
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1607,34 +1607,34 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2" t="n">
         <v>1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -1649,7 +1649,7 @@
         <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
@@ -1658,10 +1658,10 @@
         <v>1</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -1670,25 +1670,25 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
         <v>1</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW2" t="n">
         <v>1</v>
@@ -1703,34 +1703,34 @@
         <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
         <v>1</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK2" t="n">
         <v>1</v>
@@ -1739,103 +1739,103 @@
         <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.698956780923994</v>
+        <v>2.429210134128167</v>
       </c>
       <c r="BN2" t="n">
-        <v>3.628315946348734</v>
+        <v>2.283755588673622</v>
       </c>
       <c r="BO2" t="n">
-        <v>31.09985096870344</v>
+        <v>27.40506706408346</v>
       </c>
       <c r="BP2" t="n">
-        <v>10.36661698956781</v>
+        <v>7.993144560357676</v>
       </c>
       <c r="BQ2" t="n">
-        <v>130.101043219076</v>
+        <v>95.53710879284651</v>
       </c>
       <c r="BR2" t="n">
-        <v>29.54485842026826</v>
+        <v>20.5538002980626</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.774962742175859</v>
+        <v>10.6575260804769</v>
       </c>
       <c r="BT2" t="n">
-        <v>35.24649776453056</v>
+        <v>33.87570789865872</v>
       </c>
       <c r="BU2" t="n">
-        <v>1509.379433681073</v>
+        <v>1200.494187779434</v>
       </c>
       <c r="BV2" t="n">
-        <v>46.13144560357676</v>
+        <v>32.73383010432191</v>
       </c>
       <c r="BW2" t="n">
-        <v>23.32488822652758</v>
+        <v>15.22503725782414</v>
       </c>
       <c r="BX2" t="n">
-        <v>25.91654247391953</v>
+        <v>26.64381520119225</v>
       </c>
       <c r="BY2" t="n">
-        <v>73.60298062593145</v>
+        <v>58.61639344262296</v>
       </c>
       <c r="BZ2" t="n">
-        <v>8.293293591654249</v>
+        <v>3.045007451564829</v>
       </c>
       <c r="CA2" t="n">
-        <v>13.99493293591655</v>
+        <v>13.32190760059613</v>
       </c>
       <c r="CB2" t="n">
-        <v>39.39314456035768</v>
+        <v>31.21132637853949</v>
       </c>
       <c r="CC2" t="n">
-        <v>160.1642324888227</v>
+        <v>110.7621460506707</v>
       </c>
       <c r="CD2" t="n">
-        <v>1216.004172876304</v>
+        <v>972.8798807749628</v>
       </c>
       <c r="CE2" t="n">
-        <v>999.8602086438154</v>
+        <v>820.2488822652758</v>
       </c>
       <c r="CF2" t="n">
-        <v>212.4119821162445</v>
+        <v>159.5203278688525</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.2703060199202919</v>
+        <v>0.1793624180919263</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.8175633270618807</v>
+        <v>0.5071236368367515</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.4723677506464393</v>
+        <v>0.2936257185437514</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.051613550384042</v>
+        <v>0.7403256753182239</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.06800608191994142</v>
+        <v>0.06399099403252982</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.3556215636544847</v>
+        <v>0.2219221921806872</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.124119821162445</v>
+        <v>1.595203278688525</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.26957400274837</v>
+        <v>1.091350949675967</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.1656948934389418</v>
+        <v>0.1006896694455713</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.307867897600476</v>
+        <v>0.9568784089808223</v>
       </c>
       <c r="CQ2" t="n">
-        <v>1.313360592199274</v>
+        <v>0.9588613952542794</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.08422856987940448</v>
+        <v>0.08416472441374698</v>
       </c>
       <c r="CS2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CT2" t="n">
         <v>1</v>
@@ -1844,19 +1844,19 @@
         <v>0</v>
       </c>
       <c r="CV2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CX2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
         <v>0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
@@ -1871,16 +1871,16 @@
         <v>1</v>
       </c>
       <c r="DE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG2" t="n">
         <v>1</v>
       </c>
       <c r="DH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
@@ -1889,7 +1889,7 @@
         <v>0</v>
       </c>
       <c r="DK2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DL2" t="n">
         <v>0</v>
@@ -1898,34 +1898,34 @@
         <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV2" t="n">
         <v>1</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DX2" t="n">
         <v>1</v>
@@ -1937,22 +1937,22 @@
         <v>0</v>
       </c>
       <c r="EA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EC2" t="n">
         <v>0</v>
       </c>
       <c r="ED2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EE2" t="n">
         <v>1</v>
       </c>
       <c r="EF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
         <v>0</v>
@@ -1961,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EJ2" t="n">
         <v>1</v>
@@ -1985,13 +1985,13 @@
         <v>1</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ER2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ES2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ET2" t="n">
         <v>1</v>
@@ -2003,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EX2" t="n">
         <v>0</v>
@@ -2015,453 +2015,899 @@
         <v>1</v>
       </c>
       <c r="FA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FB2" t="n">
         <v>0</v>
       </c>
       <c r="FC2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FD2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>1.445603576751118</v>
+        <v>1.855439642324888</v>
       </c>
       <c r="FF2" t="n">
-        <v>2.600298062593145</v>
+        <v>2.105514157973175</v>
       </c>
       <c r="FG2" t="n">
-        <v>19.93561847988078</v>
+        <v>40.53114754098361</v>
       </c>
       <c r="FH2" t="n">
-        <v>6.934128166915054</v>
+        <v>10.52757078986587</v>
       </c>
       <c r="FI2" t="n">
-        <v>121.3472429210134</v>
+        <v>140.0166915052161</v>
       </c>
       <c r="FJ2" t="n">
-        <v>27.30312965722802</v>
+        <v>36.32011922503727</v>
       </c>
       <c r="FK2" t="n">
-        <v>7.367511177347244</v>
+        <v>20.00238450074516</v>
       </c>
       <c r="FL2" t="n">
-        <v>35.97078986587184</v>
+        <v>58.42801788375559</v>
       </c>
       <c r="FM2" t="n">
-        <v>1375.557675111774</v>
+        <v>1639.66915052161</v>
       </c>
       <c r="FN2" t="n">
-        <v>32.07034277198213</v>
+        <v>43.68941877794337</v>
       </c>
       <c r="FO2" t="n">
-        <v>20.36900149031297</v>
+        <v>15.79135618479881</v>
       </c>
       <c r="FP2" t="n">
-        <v>21.23576751117735</v>
+        <v>35.26736214605067</v>
       </c>
       <c r="FQ2" t="n">
-        <v>52.0059612518629</v>
+        <v>60.53353204172877</v>
       </c>
       <c r="FR2" t="n">
-        <v>4.333830104321908</v>
+        <v>2.631892697466468</v>
       </c>
       <c r="FS2" t="n">
-        <v>20.80238450074516</v>
+        <v>18.94962742175857</v>
       </c>
       <c r="FT2" t="n">
-        <v>32.50372578241431</v>
+        <v>50.53233979135619</v>
       </c>
       <c r="FU2" t="n">
-        <v>133.4819672131148</v>
+        <v>132.64739195231</v>
       </c>
       <c r="FV2" t="n">
-        <v>1147.598211624441</v>
+        <v>1341.738897168406</v>
       </c>
       <c r="FW2" t="n">
-        <v>949.1087928464979</v>
+        <v>1119.080774962742</v>
       </c>
       <c r="FX2" t="n">
-        <v>176.7335916542474</v>
+        <v>219.6577645305515</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.3069796323894685</v>
+        <v>0.1346007593995671</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.7493914555389967</v>
+        <v>0.6728401983841626</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.1004083348345644</v>
+        <v>0.3120030061013668</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.5891087330729655</v>
+        <v>0.6483004063331933</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.06716802195214294</v>
+        <v>0.1100839642917685</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.2692605388651058</v>
+        <v>0.26391940224205</v>
       </c>
       <c r="GE2" t="n">
-        <v>1.767335916542474</v>
+        <v>2.196577645305514</v>
       </c>
       <c r="GF2" t="n">
-        <v>1.017062115854787</v>
+        <v>1.361377150559232</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.1300477960858356</v>
+        <v>0.1345120987583533</v>
       </c>
       <c r="GH2" t="n">
-        <v>1.208266551003037</v>
+        <v>1.40261489628809</v>
       </c>
       <c r="GI2" t="n">
-        <v>1.185764913533611</v>
+        <v>1.374386701983738</v>
       </c>
       <c r="GJ2" t="n">
-        <v>0.08208320031475307</v>
+        <v>0.1490970282461112</v>
       </c>
       <c r="GK2" t="n">
-        <v>1.028017883755589</v>
+        <v>0.1782414307004467</v>
       </c>
       <c r="GL2" t="n">
-        <v>11.16423248882266</v>
+        <v>-13.12608047690015</v>
       </c>
       <c r="GM2" t="n">
-        <v>3.432488822652758</v>
+        <v>-2.534426229508197</v>
       </c>
       <c r="GN2" t="n">
-        <v>8.753800298062615</v>
+        <v>-44.47958271236962</v>
       </c>
       <c r="GO2" t="n">
-        <v>2.241728763040243</v>
+        <v>-15.76631892697467</v>
       </c>
       <c r="GP2" t="n">
-        <v>0.407451564828615</v>
+        <v>-9.344858420268258</v>
       </c>
       <c r="GQ2" t="n">
-        <v>-0.724292101341284</v>
+        <v>-24.55230998509687</v>
       </c>
       <c r="GR2" t="n">
-        <v>133.8217585692998</v>
+        <v>-439.1749627421759</v>
       </c>
       <c r="GS2" t="n">
-        <v>14.06110283159464</v>
+        <v>-10.95558867362146</v>
       </c>
       <c r="GT2" t="n">
-        <v>2.955886736214605</v>
+        <v>-0.5663189269746649</v>
       </c>
       <c r="GU2" t="n">
-        <v>4.680774962742174</v>
+        <v>-8.623546944858418</v>
       </c>
       <c r="GV2" t="n">
-        <v>21.59701937406855</v>
+        <v>-1.917138599105812</v>
       </c>
       <c r="GW2" t="n">
-        <v>3.959463487332341</v>
+        <v>0.4131147540983608</v>
       </c>
       <c r="GX2" t="n">
-        <v>-6.807451564828613</v>
+        <v>-5.627719821162444</v>
       </c>
       <c r="GY2" t="n">
-        <v>6.889418777943369</v>
+        <v>-19.32101341281669</v>
       </c>
       <c r="GZ2" t="n">
-        <v>26.68226527570789</v>
+        <v>-21.88524590163934</v>
       </c>
       <c r="HA2" t="n">
-        <v>68.40596125186289</v>
+        <v>-368.8590163934429</v>
       </c>
       <c r="HB2" t="n">
-        <v>50.75141579731758</v>
+        <v>-298.8318926974664</v>
       </c>
       <c r="HC2" t="n">
-        <v>35.67839046199708</v>
+        <v>-60.13743666169898</v>
       </c>
       <c r="HD2" t="n">
-        <v>-0.03667361246917661</v>
+        <v>0.04476165869235915</v>
       </c>
       <c r="HE2" t="n">
-        <v>0.06817187152288406</v>
+        <v>-0.1657165615474111</v>
       </c>
       <c r="HF2" t="n">
-        <v>0.3719594158118749</v>
+        <v>-0.01837728755761536</v>
       </c>
       <c r="HG2" t="n">
-        <v>0.462504817311077</v>
+        <v>0.09202526898503061</v>
       </c>
       <c r="HH2" t="n">
-        <v>0.0008380599677984824</v>
+        <v>-0.04609297025923872</v>
       </c>
       <c r="HI2" t="n">
-        <v>0.0863610247893789</v>
+        <v>-0.04199721006136281</v>
       </c>
       <c r="HJ2" t="n">
-        <v>0.3567839046199701</v>
+        <v>-0.6013743666169893</v>
       </c>
       <c r="HK2" t="n">
-        <v>0.2525118868935825</v>
+        <v>-0.2700262008832646</v>
       </c>
       <c r="HL2" t="n">
-        <v>0.03564709735310617</v>
+        <v>-0.03382242931278201</v>
       </c>
       <c r="HM2" t="n">
-        <v>0.09960134659743858</v>
+        <v>-0.4457364873072672</v>
       </c>
       <c r="HN2" t="n">
-        <v>0.1275956786656631</v>
+        <v>-0.415525306729459</v>
       </c>
       <c r="HO2" t="n">
-        <v>0.002145369564651417</v>
+        <v>-0.06493230383236423</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
-      <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr"/>
-      <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr"/>
-      <c r="BW3" t="inlineStr"/>
-      <c r="BX3" t="inlineStr"/>
-      <c r="BY3" t="inlineStr"/>
-      <c r="BZ3" t="inlineStr"/>
-      <c r="CA3" t="inlineStr"/>
-      <c r="CB3" t="inlineStr"/>
-      <c r="CC3" t="inlineStr"/>
-      <c r="CD3" t="inlineStr"/>
-      <c r="CE3" t="inlineStr"/>
-      <c r="CF3" t="inlineStr"/>
-      <c r="CG3" t="inlineStr"/>
-      <c r="CH3" t="inlineStr"/>
-      <c r="CI3" t="inlineStr"/>
-      <c r="CJ3" t="inlineStr"/>
-      <c r="CK3" t="inlineStr"/>
-      <c r="CL3" t="inlineStr"/>
-      <c r="CM3" t="inlineStr"/>
-      <c r="CN3" t="inlineStr"/>
-      <c r="CO3" t="inlineStr"/>
-      <c r="CP3" t="inlineStr"/>
-      <c r="CQ3" t="inlineStr"/>
-      <c r="CR3" t="inlineStr"/>
-      <c r="CS3" t="inlineStr"/>
-      <c r="CT3" t="inlineStr"/>
-      <c r="CU3" t="inlineStr"/>
-      <c r="CV3" t="inlineStr"/>
-      <c r="CW3" t="inlineStr"/>
-      <c r="CX3" t="inlineStr"/>
-      <c r="CY3" t="inlineStr"/>
-      <c r="CZ3" t="inlineStr"/>
-      <c r="DA3" t="inlineStr"/>
-      <c r="DB3" t="inlineStr"/>
-      <c r="DC3" t="inlineStr"/>
-      <c r="DD3" t="inlineStr"/>
-      <c r="DE3" t="inlineStr"/>
-      <c r="DF3" t="inlineStr"/>
-      <c r="DG3" t="inlineStr"/>
-      <c r="DH3" t="inlineStr"/>
-      <c r="DI3" t="inlineStr"/>
-      <c r="DJ3" t="inlineStr"/>
-      <c r="DK3" t="inlineStr"/>
-      <c r="DL3" t="inlineStr"/>
-      <c r="DM3" t="inlineStr"/>
-      <c r="DN3" t="inlineStr"/>
-      <c r="DO3" t="inlineStr"/>
-      <c r="DP3" t="inlineStr"/>
-      <c r="DQ3" t="inlineStr"/>
-      <c r="DR3" t="inlineStr"/>
-      <c r="DS3" t="inlineStr"/>
-      <c r="DT3" t="inlineStr"/>
-      <c r="DU3" t="inlineStr"/>
-      <c r="DV3" t="inlineStr"/>
-      <c r="DW3" t="inlineStr"/>
-      <c r="DX3" t="inlineStr"/>
-      <c r="DY3" t="inlineStr"/>
-      <c r="DZ3" t="inlineStr"/>
-      <c r="EA3" t="inlineStr"/>
-      <c r="EB3" t="inlineStr"/>
-      <c r="EC3" t="inlineStr"/>
-      <c r="ED3" t="inlineStr"/>
-      <c r="EE3" t="inlineStr"/>
-      <c r="EF3" t="inlineStr"/>
-      <c r="EG3" t="inlineStr"/>
-      <c r="EH3" t="inlineStr"/>
-      <c r="EI3" t="inlineStr"/>
-      <c r="EJ3" t="inlineStr"/>
-      <c r="EK3" t="inlineStr"/>
-      <c r="EL3" t="inlineStr"/>
-      <c r="EM3" t="inlineStr"/>
-      <c r="EN3" t="inlineStr"/>
-      <c r="EO3" t="inlineStr"/>
-      <c r="EP3" t="inlineStr"/>
-      <c r="EQ3" t="inlineStr"/>
-      <c r="ER3" t="inlineStr"/>
-      <c r="ES3" t="inlineStr"/>
-      <c r="ET3" t="inlineStr"/>
-      <c r="EU3" t="inlineStr"/>
-      <c r="EV3" t="inlineStr"/>
-      <c r="EW3" t="inlineStr"/>
-      <c r="EX3" t="inlineStr"/>
-      <c r="EY3" t="inlineStr"/>
-      <c r="EZ3" t="inlineStr"/>
-      <c r="FA3" t="inlineStr"/>
-      <c r="FB3" t="inlineStr"/>
-      <c r="FC3" t="inlineStr"/>
-      <c r="FD3" t="inlineStr"/>
-      <c r="FE3" t="inlineStr"/>
-      <c r="FF3" t="inlineStr"/>
-      <c r="FG3" t="inlineStr"/>
-      <c r="FH3" t="inlineStr"/>
-      <c r="FI3" t="inlineStr"/>
-      <c r="FJ3" t="inlineStr"/>
-      <c r="FK3" t="inlineStr"/>
-      <c r="FL3" t="inlineStr"/>
-      <c r="FM3" t="inlineStr"/>
-      <c r="FN3" t="inlineStr"/>
-      <c r="FO3" t="inlineStr"/>
-      <c r="FP3" t="inlineStr"/>
-      <c r="FQ3" t="inlineStr"/>
-      <c r="FR3" t="inlineStr"/>
-      <c r="FS3" t="inlineStr"/>
-      <c r="FT3" t="inlineStr"/>
-      <c r="FU3" t="inlineStr"/>
-      <c r="FV3" t="inlineStr"/>
-      <c r="FW3" t="inlineStr"/>
-      <c r="FX3" t="inlineStr"/>
-      <c r="FY3" t="inlineStr"/>
-      <c r="FZ3" t="inlineStr"/>
-      <c r="GA3" t="inlineStr"/>
-      <c r="GB3" t="inlineStr"/>
-      <c r="GC3" t="inlineStr"/>
-      <c r="GD3" t="inlineStr"/>
-      <c r="GE3" t="inlineStr"/>
-      <c r="GF3" t="inlineStr"/>
-      <c r="GG3" t="inlineStr"/>
-      <c r="GH3" t="inlineStr"/>
-      <c r="GI3" t="inlineStr"/>
-      <c r="GJ3" t="inlineStr"/>
-      <c r="GK3" t="inlineStr"/>
-      <c r="GL3" t="inlineStr"/>
-      <c r="GM3" t="inlineStr"/>
-      <c r="GN3" t="inlineStr"/>
-      <c r="GO3" t="inlineStr"/>
-      <c r="GP3" t="inlineStr"/>
-      <c r="GQ3" t="inlineStr"/>
-      <c r="GR3" t="inlineStr"/>
-      <c r="GS3" t="inlineStr"/>
-      <c r="GT3" t="inlineStr"/>
-      <c r="GU3" t="inlineStr"/>
-      <c r="GV3" t="inlineStr"/>
-      <c r="GW3" t="inlineStr"/>
-      <c r="GX3" t="inlineStr"/>
-      <c r="GY3" t="inlineStr"/>
-      <c r="GZ3" t="inlineStr"/>
-      <c r="HA3" t="inlineStr"/>
-      <c r="HB3" t="inlineStr"/>
-      <c r="HC3" t="inlineStr"/>
-      <c r="HD3" t="inlineStr"/>
-      <c r="HE3" t="inlineStr"/>
-      <c r="HF3" t="inlineStr"/>
-      <c r="HG3" t="inlineStr"/>
-      <c r="HH3" t="inlineStr"/>
-      <c r="HI3" t="inlineStr"/>
-      <c r="HJ3" t="inlineStr"/>
-      <c r="HK3" t="inlineStr"/>
-      <c r="HL3" t="inlineStr"/>
-      <c r="HM3" t="inlineStr"/>
-      <c r="HN3" t="inlineStr"/>
-      <c r="HO3" t="inlineStr"/>
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.445603576751118</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0.9335320417287631</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>21.93800298062594</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>8.401788375558869</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>110.1567809239941</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>20.53770491803279</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>8.401788375558869</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>35.474217585693</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>1335.88435171386</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>35.00745156482862</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>18.20387481371088</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>20.53770491803279</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>52.27779433681074</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>2.800596125186289</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>21.47123695976155</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>42.00894187779434</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>134.8953800298063</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>1091.765722801789</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>899.4581222056632</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>191.9341877794337</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0.1025859386515124</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0.9573832724652397</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0.4096013563658085</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.819202712731617</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.07509034553492934</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>0.2910546700503086</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>1.919341877794337</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>0.9979885769727604</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>0.09912584235904719</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>1.098487895065769</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>1.095799591994045</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>0.09268022664954234</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CY3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DX3" t="n">
+        <v>1</v>
+      </c>
+      <c r="DY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="EB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="ED3" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="EF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="EJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="EK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="EM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="EN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="EO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="EP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="EQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="ER3" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES3" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET3" t="n">
+        <v>1</v>
+      </c>
+      <c r="EU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="EV3" t="n">
+        <v>1</v>
+      </c>
+      <c r="EW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY3" t="n">
+        <v>1</v>
+      </c>
+      <c r="EZ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="FA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="FB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="FC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="FD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE3" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="FF3" t="n">
+        <v>4.056035767511178</v>
+      </c>
+      <c r="FG3" t="n">
+        <v>19.82950819672131</v>
+      </c>
+      <c r="FH3" t="n">
+        <v>7.210730253353205</v>
+      </c>
+      <c r="FI3" t="n">
+        <v>75.71266766020865</v>
+      </c>
+      <c r="FJ3" t="n">
+        <v>30.64560357675112</v>
+      </c>
+      <c r="FK3" t="n">
+        <v>4.506706408345753</v>
+      </c>
+      <c r="FL3" t="n">
+        <v>22.08286140089419</v>
+      </c>
+      <c r="FM3" t="n">
+        <v>954.0697466467959</v>
+      </c>
+      <c r="FN3" t="n">
+        <v>41.46169895678093</v>
+      </c>
+      <c r="FO3" t="n">
+        <v>17.57615499254844</v>
+      </c>
+      <c r="FP3" t="n">
+        <v>27.04023845007452</v>
+      </c>
+      <c r="FQ3" t="n">
+        <v>77.06467958271239</v>
+      </c>
+      <c r="FR3" t="n">
+        <v>5.408047690014904</v>
+      </c>
+      <c r="FS3" t="n">
+        <v>27.49090909090909</v>
+      </c>
+      <c r="FT3" t="n">
+        <v>33.34962742175858</v>
+      </c>
+      <c r="FU3" t="n">
+        <v>138.3558867362146</v>
+      </c>
+      <c r="FV3" t="n">
+        <v>679.6113263785396</v>
+      </c>
+      <c r="FW3" t="n">
+        <v>483.5695976154993</v>
+      </c>
+      <c r="FX3" t="n">
+        <v>158.3656631892698</v>
+      </c>
+      <c r="FY3" t="n">
+        <v>0.5021758569299554</v>
+      </c>
+      <c r="FZ3" t="n">
+        <v>0.8650535157837691</v>
+      </c>
+      <c r="GA3" t="n">
+        <v>0.2506889831479996</v>
+      </c>
+      <c r="GB3" t="n">
+        <v>0.7544674997134014</v>
+      </c>
+      <c r="GC3" t="n">
+        <v>0.07297260314569258</v>
+      </c>
+      <c r="GD3" t="n">
+        <v>0.4824428030894866</v>
+      </c>
+      <c r="GE3" t="n">
+        <v>1.583656631892698</v>
+      </c>
+      <c r="GF3" t="n">
+        <v>0.9681240470574815</v>
+      </c>
+      <c r="GG3" t="n">
+        <v>0.098332669651508</v>
+      </c>
+      <c r="GH3" t="n">
+        <v>0.7575217638381982</v>
+      </c>
+      <c r="GI3" t="n">
+        <v>0.8396398900537603</v>
+      </c>
+      <c r="GJ3" t="n">
+        <v>0.08694881036703256</v>
+      </c>
+      <c r="GK3" t="n">
+        <v>-3.122503725782415</v>
+      </c>
+      <c r="GL3" t="n">
+        <v>2.108494783904622</v>
+      </c>
+      <c r="GM3" t="n">
+        <v>1.191058122205664</v>
+      </c>
+      <c r="GN3" t="n">
+        <v>34.44411326378541</v>
+      </c>
+      <c r="GO3" t="n">
+        <v>-10.10789865871833</v>
+      </c>
+      <c r="GP3" t="n">
+        <v>3.895081967213116</v>
+      </c>
+      <c r="GQ3" t="n">
+        <v>13.39135618479881</v>
+      </c>
+      <c r="GR3" t="n">
+        <v>381.8146050670641</v>
+      </c>
+      <c r="GS3" t="n">
+        <v>-6.454247391952308</v>
+      </c>
+      <c r="GT3" t="n">
+        <v>0.6277198211624473</v>
+      </c>
+      <c r="GU3" t="n">
+        <v>-6.502533532041728</v>
+      </c>
+      <c r="GV3" t="n">
+        <v>-24.78688524590165</v>
+      </c>
+      <c r="GW3" t="n">
+        <v>-2.607451564828614</v>
+      </c>
+      <c r="GX3" t="n">
+        <v>-6.019672131147541</v>
+      </c>
+      <c r="GY3" t="n">
+        <v>8.659314456035766</v>
+      </c>
+      <c r="GZ3" t="n">
+        <v>-3.460506706408353</v>
+      </c>
+      <c r="HA3" t="n">
+        <v>412.154396423249</v>
+      </c>
+      <c r="HB3" t="n">
+        <v>415.888524590164</v>
+      </c>
+      <c r="HC3" t="n">
+        <v>33.56852459016395</v>
+      </c>
+      <c r="HD3" t="n">
+        <v>-0.3995899182784429</v>
+      </c>
+      <c r="HE3" t="n">
+        <v>0.09232975668147059</v>
+      </c>
+      <c r="HF3" t="n">
+        <v>0.1589123732178089</v>
+      </c>
+      <c r="HG3" t="n">
+        <v>0.06473521301821561</v>
+      </c>
+      <c r="HH3" t="n">
+        <v>0.00211774238923676</v>
+      </c>
+      <c r="HI3" t="n">
+        <v>-0.191388133039178</v>
+      </c>
+      <c r="HJ3" t="n">
+        <v>0.3356852459016393</v>
+      </c>
+      <c r="HK3" t="n">
+        <v>0.02986452991527899</v>
+      </c>
+      <c r="HL3" t="n">
+        <v>0.0007931727075391887</v>
+      </c>
+      <c r="HM3" t="n">
+        <v>0.340966131227571</v>
+      </c>
+      <c r="HN3" t="n">
+        <v>0.256159701940285</v>
+      </c>
+      <c r="HO3" t="n">
+        <v>0.005731416282509783</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -2470,16 +2916,16 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -2500,16 +2946,16 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -2518,13 +2964,13 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
         <v>1</v>
@@ -2533,13 +2979,13 @@
         <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -2563,13 +3009,13 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR4" t="n">
         <v>1</v>
@@ -2578,7 +3024,7 @@
         <v>1</v>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
         <v>1</v>
@@ -2587,25 +3033,25 @@
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA4" t="n">
         <v>1</v>
       </c>
       <c r="BB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD4" t="n">
         <v>0</v>
@@ -2617,118 +3063,118 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.855439642324888</v>
+        <v>1.780923994038748</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.550223546944859</v>
+        <v>2.400894187779434</v>
       </c>
       <c r="BO4" t="n">
-        <v>29.32757078986588</v>
+        <v>22.56840536512668</v>
       </c>
       <c r="BP4" t="n">
-        <v>9.775856929955291</v>
+        <v>7.68286140089419</v>
       </c>
       <c r="BQ4" t="n">
-        <v>109.2345752608048</v>
+        <v>115.2429210134129</v>
       </c>
       <c r="BR4" t="n">
-        <v>26.35230998509687</v>
+        <v>37.45394932935918</v>
       </c>
       <c r="BS4" t="n">
-        <v>14.87630402384501</v>
+        <v>11.52429210134128</v>
       </c>
       <c r="BT4" t="n">
-        <v>38.67839046199703</v>
+        <v>40.81520119225038</v>
       </c>
       <c r="BU4" t="n">
-        <v>1301.464083457526</v>
+        <v>1369.470044709389</v>
       </c>
       <c r="BV4" t="n">
-        <v>35.27809239940388</v>
+        <v>47.5377049180328</v>
       </c>
       <c r="BW4" t="n">
-        <v>13.60119225037258</v>
+        <v>21.12786885245902</v>
       </c>
       <c r="BX4" t="n">
-        <v>25.92727272727273</v>
+        <v>50.41877794336812</v>
       </c>
       <c r="BY4" t="n">
-        <v>51.85454545454546</v>
+        <v>74.90789865871835</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.125186289120716</v>
+        <v>3.841430700447095</v>
       </c>
       <c r="CA4" t="n">
-        <v>13.60119225037258</v>
+        <v>26.40983606557378</v>
       </c>
       <c r="CB4" t="n">
-        <v>41.65365126676603</v>
+        <v>45.13681073025337</v>
       </c>
       <c r="CC4" t="n">
-        <v>102.0089418777943</v>
+        <v>163.7409836065574</v>
       </c>
       <c r="CD4" t="n">
-        <v>1053.667362146051</v>
+        <v>1073.679880774963</v>
       </c>
       <c r="CE4" t="n">
-        <v>883.6524590163935</v>
+        <v>822.0661698956783</v>
       </c>
       <c r="CF4" t="n">
-        <v>178.2606259314456</v>
+        <v>182.8521013412818</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.1804462204462204</v>
+        <v>0.3410500974435402</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.6675005140578911</v>
+        <v>0.8541922607943475</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.2932575439132816</v>
+        <v>0.1558926470423451</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.6002288967862739</v>
+        <v>0.7943259135170269</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.07648052395196415</v>
+        <v>0.08709159093464779</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.2089374685609396</v>
+        <v>0.3733528760009198</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.782606259314456</v>
+        <v>1.828521013412818</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.117792239947496</v>
+        <v>1.269800619440865</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.1048000603151021</v>
+        <v>0.1468585676308214</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.091274319668427</v>
+        <v>1.153305569109499</v>
       </c>
       <c r="CQ4" t="n">
-        <v>1.083420195236917</v>
+        <v>1.173858939385569</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.1066902822381669</v>
+        <v>0.1127061067773567</v>
       </c>
       <c r="CS4" t="n">
         <v>0</v>
@@ -2737,7 +3183,7 @@
         <v>1</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV4" t="n">
         <v>0</v>
@@ -2749,7 +3195,7 @@
         <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CZ4" t="n">
         <v>1</v>
@@ -2761,13 +3207,13 @@
         <v>1</v>
       </c>
       <c r="DC4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DE4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2788,7 +3234,7 @@
         <v>1</v>
       </c>
       <c r="DL4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM4" t="n">
         <v>1</v>
@@ -2797,16 +3243,16 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2818,7 +3264,7 @@
         <v>1</v>
       </c>
       <c r="DV4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
@@ -2827,10 +3273,10 @@
         <v>1</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EA4" t="n">
         <v>1</v>
@@ -2839,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ED4" t="n">
         <v>0</v>
@@ -2848,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="EF4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EI4" t="n">
         <v>1</v>
@@ -2866,7 +3312,7 @@
         <v>1</v>
       </c>
       <c r="EL4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
         <v>0</v>
@@ -2875,37 +3321,37 @@
         <v>0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EP4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ES4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ET4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EU4" t="n">
         <v>1</v>
       </c>
       <c r="EV4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EW4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EX4" t="n">
         <v>1</v>
       </c>
       <c r="EY4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EZ4" t="n">
         <v>1</v>
@@ -2914,202 +3360,202 @@
         <v>1</v>
       </c>
       <c r="FB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FD4" t="n">
         <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>3.979135618479881</v>
+        <v>1.698956780923994</v>
       </c>
       <c r="FF4" t="n">
-        <v>3.469448584202683</v>
+        <v>3.75290611028316</v>
       </c>
       <c r="FG4" t="n">
-        <v>31.57198211624441</v>
+        <v>25.43636363636364</v>
       </c>
       <c r="FH4" t="n">
-        <v>11.79612518628912</v>
+        <v>9.173770491803282</v>
       </c>
       <c r="FI4" t="n">
-        <v>110.3284649776453</v>
+        <v>111.3362146050671</v>
       </c>
       <c r="FJ4" t="n">
-        <v>14.91862891207154</v>
+        <v>30.44023845007452</v>
       </c>
       <c r="FK4" t="n">
-        <v>13.18390461997019</v>
+        <v>6.671833084947841</v>
       </c>
       <c r="FL4" t="n">
-        <v>28.10253353204173</v>
+        <v>34.61013412816693</v>
       </c>
       <c r="FM4" t="n">
-        <v>1378.064977645306</v>
+        <v>1255.138599105813</v>
       </c>
       <c r="FN4" t="n">
-        <v>28.79642324888227</v>
+        <v>39.61400894187781</v>
       </c>
       <c r="FO4" t="n">
-        <v>13.53084947839046</v>
+        <v>16.26259314456036</v>
       </c>
       <c r="FP4" t="n">
-        <v>15.61251862891207</v>
+        <v>25.85335320417288</v>
       </c>
       <c r="FQ4" t="n">
-        <v>25.32697466467959</v>
+        <v>61.29746646795828</v>
       </c>
       <c r="FR4" t="n">
-        <v>3.122503725782415</v>
+        <v>6.671833084947841</v>
       </c>
       <c r="FS4" t="n">
-        <v>9.367511177347245</v>
+        <v>10.00774962742176</v>
       </c>
       <c r="FT4" t="n">
-        <v>27.75558867362146</v>
+        <v>36.27809239940388</v>
       </c>
       <c r="FU4" t="n">
-        <v>79.45037257824144</v>
+        <v>125.9308494783905</v>
       </c>
       <c r="FV4" t="n">
-        <v>1191.408643815201</v>
+        <v>1008.280774962742</v>
       </c>
       <c r="FW4" t="n">
-        <v>1065.467660208644</v>
+        <v>829.8092399403877</v>
       </c>
       <c r="FX4" t="n">
-        <v>154.8414903129658</v>
+        <v>171.1325186289121</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.1908850840576974</v>
+        <v>0.336597105883509</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.6499459845843646</v>
+        <v>0.7669292616737171</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.03854942871336314</v>
+        <v>0.4946850599309617</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.3854942871336315</v>
+        <v>0.8564324200389775</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.04123781940612487</v>
+        <v>0.06832830676812324</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.1164070447624805</v>
+        <v>0.2689247376860569</v>
       </c>
       <c r="GE4" t="n">
-        <v>1.548414903129657</v>
+        <v>1.711325186289121</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.8990869304273357</v>
+        <v>1.101543970187785</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.1089308718497888</v>
+        <v>0.1456311828975673</v>
       </c>
       <c r="GH4" t="n">
-        <v>1.101134275210998</v>
+        <v>1.117428806887804</v>
       </c>
       <c r="GI4" t="n">
-        <v>1.06121448644713</v>
+        <v>1.109488440650898</v>
       </c>
       <c r="GJ4" t="n">
-        <v>0.06016271384041376</v>
+        <v>0.08214752227489447</v>
       </c>
       <c r="GK4" t="n">
-        <v>-0.9192250372578243</v>
+        <v>-1.352011922503726</v>
       </c>
       <c r="GL4" t="n">
-        <v>-2.244411326378536</v>
+        <v>-2.867958271236958</v>
       </c>
       <c r="GM4" t="n">
-        <v>-2.02026825633383</v>
+        <v>-1.490909090909092</v>
       </c>
       <c r="GN4" t="n">
-        <v>-1.09388971684055</v>
+        <v>3.906706408345769</v>
       </c>
       <c r="GO4" t="n">
-        <v>11.43368107302534</v>
+        <v>7.013710879284655</v>
       </c>
       <c r="GP4" t="n">
-        <v>1.692399403874814</v>
+        <v>4.852459016393444</v>
       </c>
       <c r="GQ4" t="n">
-        <v>10.57585692995529</v>
+        <v>6.205067064083458</v>
       </c>
       <c r="GR4" t="n">
-        <v>-76.60089418777943</v>
+        <v>114.3314456035766</v>
       </c>
       <c r="GS4" t="n">
-        <v>6.481669150521611</v>
+        <v>7.923695976154995</v>
       </c>
       <c r="GT4" t="n">
-        <v>0.07034277198211747</v>
+        <v>4.865275707898661</v>
       </c>
       <c r="GU4" t="n">
-        <v>10.31475409836066</v>
+        <v>24.56542473919524</v>
       </c>
       <c r="GV4" t="n">
-        <v>26.52757078986587</v>
+        <v>13.61043219076007</v>
       </c>
       <c r="GW4" t="n">
-        <v>-0.997317436661699</v>
+        <v>-2.830402384500746</v>
       </c>
       <c r="GX4" t="n">
-        <v>4.233681073025336</v>
+        <v>16.40208643815202</v>
       </c>
       <c r="GY4" t="n">
-        <v>13.89806259314456</v>
+        <v>8.858718330849484</v>
       </c>
       <c r="GZ4" t="n">
-        <v>22.5585692995529</v>
+        <v>37.81013412816694</v>
       </c>
       <c r="HA4" t="n">
-        <v>-137.7412816691503</v>
+        <v>65.39910581222057</v>
       </c>
       <c r="HB4" t="n">
-        <v>-181.8152011922505</v>
+        <v>-7.743070044709384</v>
       </c>
       <c r="HC4" t="n">
-        <v>23.41913561847986</v>
+        <v>11.71958271236966</v>
       </c>
       <c r="HD4" t="n">
-        <v>-0.01043886361147697</v>
+        <v>0.004452991560031205</v>
       </c>
       <c r="HE4" t="n">
-        <v>0.01755452947352654</v>
+        <v>0.0872629991206304</v>
       </c>
       <c r="HF4" t="n">
-        <v>0.2547081151999185</v>
+        <v>-0.3387924128886166</v>
       </c>
       <c r="HG4" t="n">
-        <v>0.2147346096526424</v>
+        <v>-0.0621065065219506</v>
       </c>
       <c r="HH4" t="n">
-        <v>0.03524270454583928</v>
+        <v>0.01876328416652455</v>
       </c>
       <c r="HI4" t="n">
-        <v>0.09253042379845906</v>
+        <v>0.1044281383148629</v>
       </c>
       <c r="HJ4" t="n">
-        <v>0.2341913561847988</v>
+        <v>0.1171958271236966</v>
       </c>
       <c r="HK4" t="n">
-        <v>0.2187053095201601</v>
+        <v>0.1682566492530797</v>
       </c>
       <c r="HL4" t="n">
-        <v>-0.004130811534686765</v>
+        <v>0.001227384733254039</v>
       </c>
       <c r="HM4" t="n">
-        <v>-0.009859955542571353</v>
+        <v>0.03587676222169467</v>
       </c>
       <c r="HN4" t="n">
-        <v>0.02220570878978712</v>
+        <v>0.06437049873467071</v>
       </c>
       <c r="HO4" t="n">
-        <v>0.04652756839775313</v>
+        <v>0.03055858450246227</v>
       </c>
     </row>
     <row r="5">
@@ -3129,10 +3575,10 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -3141,7 +3587,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -3153,7 +3599,7 @@
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -3162,19 +3608,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -3189,7 +3635,7 @@
         <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -3207,19 +3653,19 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
@@ -3234,7 +3680,7 @@
         <v>1</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP5" t="n">
         <v>1</v>
@@ -3243,31 +3689,31 @@
         <v>1</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -3276,16 +3722,16 @@
         <v>1</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -3294,157 +3740,157 @@
         <v>1</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ5" t="n">
         <v>1</v>
       </c>
       <c r="BK5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
         <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.943368107302534</v>
+        <v>3.979135618479881</v>
       </c>
       <c r="BN5" t="n">
-        <v>3.398807749627422</v>
+        <v>3.532041728763041</v>
       </c>
       <c r="BO5" t="n">
-        <v>27.67600596125186</v>
+        <v>32.14157973174367</v>
       </c>
       <c r="BP5" t="n">
-        <v>7.768703427719821</v>
+        <v>12.00894187779434</v>
       </c>
       <c r="BQ5" t="n">
-        <v>100.0220566318927</v>
+        <v>103.1356184798808</v>
       </c>
       <c r="BR5" t="n">
-        <v>35.93025335320417</v>
+        <v>14.48137108792847</v>
       </c>
       <c r="BS5" t="n">
-        <v>13.59523099850969</v>
+        <v>12.36214605067064</v>
       </c>
       <c r="BT5" t="n">
-        <v>39.81460506706408</v>
+        <v>25.43070044709389</v>
       </c>
       <c r="BU5" t="n">
-        <v>1229.397317436662</v>
+        <v>1323.456035767511</v>
       </c>
       <c r="BV5" t="n">
-        <v>30.58926974664679</v>
+        <v>26.4903129657228</v>
       </c>
       <c r="BW5" t="n">
-        <v>17.4795827123696</v>
+        <v>14.12816691505216</v>
       </c>
       <c r="BX5" t="n">
-        <v>19.90730253353204</v>
+        <v>20.83904619970194</v>
       </c>
       <c r="BY5" t="n">
-        <v>49.03994038748137</v>
+        <v>34.9672131147541</v>
       </c>
       <c r="BZ5" t="n">
-        <v>6.312071535022355</v>
+        <v>3.532041728763041</v>
       </c>
       <c r="CA5" t="n">
-        <v>13.1096870342772</v>
+        <v>13.42175856929955</v>
       </c>
       <c r="CB5" t="n">
-        <v>37.87242921013413</v>
+        <v>27.19672131147541</v>
       </c>
       <c r="CC5" t="n">
-        <v>135.9523099850969</v>
+        <v>96.07153502235469</v>
       </c>
       <c r="CD5" t="n">
-        <v>971.57347242921</v>
+        <v>1117.891207153502</v>
       </c>
       <c r="CE5" t="n">
-        <v>757.934128166915</v>
+        <v>984.7332339791358</v>
       </c>
       <c r="CF5" t="n">
-        <v>187.9055141579732</v>
+        <v>152.9374068554396</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.2738965952080706</v>
+        <v>0.194328887120594</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.662746761435286</v>
+        <v>0.6616718142031547</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.2562593144560357</v>
+        <v>0.05529964322810821</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.7148286140089418</v>
+        <v>0.3817459242198438</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.1024929440693696</v>
+        <v>0.04045810159041732</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.3549589580696518</v>
+        <v>0.180323350071366</v>
       </c>
       <c r="CM5" t="n">
-        <v>1.879055141579732</v>
+        <v>1.529374068554397</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.229528672325536</v>
+        <v>0.9527686195631317</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.08587724072341778</v>
+        <v>0.09712846944911437</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.9949745246549878</v>
+        <v>1.029631810693838</v>
       </c>
       <c r="CQ5" t="n">
-        <v>1.029310790545889</v>
+        <v>1.011125174421627</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.1346732944540786</v>
+        <v>0.05983684274035909</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CU5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV5" t="n">
         <v>1</v>
       </c>
       <c r="CW5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CX5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>1</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DB5" t="n">
         <v>1</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DF5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
         <v>1</v>
@@ -3453,25 +3899,25 @@
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DK5" t="n">
         <v>1</v>
       </c>
       <c r="DL5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
         <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DO5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
@@ -3486,301 +3932,301 @@
         <v>1</v>
       </c>
       <c r="DU5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV5" t="n">
         <v>1</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DX5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC5" t="n">
         <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>1</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH5" t="n">
         <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK5" t="n">
         <v>1</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EM5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EP5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ER5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ET5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EU5" t="n">
         <v>1</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EW5" t="n">
         <v>1</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EY5" t="n">
         <v>1</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FA5" t="n">
         <v>1</v>
       </c>
       <c r="FB5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FD5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>1.780923994038748</v>
+        <v>1.84053651266766</v>
       </c>
       <c r="FF5" t="n">
-        <v>1.921013412816692</v>
+        <v>3.95230998509687</v>
       </c>
       <c r="FG5" t="n">
-        <v>21.51535022354695</v>
+        <v>18.57585692995529</v>
       </c>
       <c r="FH5" t="n">
-        <v>6.531445603576753</v>
+        <v>5.928464977645305</v>
       </c>
       <c r="FI5" t="n">
-        <v>95.28226527570793</v>
+        <v>81.41758569299553</v>
       </c>
       <c r="FJ5" t="n">
-        <v>31.12041728763041</v>
+        <v>26.08524590163934</v>
       </c>
       <c r="FK5" t="n">
-        <v>10.37347242921014</v>
+        <v>4.347540983606557</v>
       </c>
       <c r="FL5" t="n">
-        <v>36.88345752608048</v>
+        <v>33.5946348733234</v>
       </c>
       <c r="FM5" t="n">
-        <v>1085.756780923994</v>
+        <v>991.6345752608048</v>
       </c>
       <c r="FN5" t="n">
-        <v>38.0360655737705</v>
+        <v>30.03755588673621</v>
       </c>
       <c r="FO5" t="n">
-        <v>14.59970193740686</v>
+        <v>8.695081967213115</v>
       </c>
       <c r="FP5" t="n">
-        <v>37.65186289120717</v>
+        <v>26.87570789865872</v>
       </c>
       <c r="FQ5" t="n">
-        <v>53.40417287630404</v>
+        <v>56.51803278688525</v>
       </c>
       <c r="FR5" t="n">
-        <v>2.689418777943369</v>
+        <v>1.580923994038748</v>
       </c>
       <c r="FS5" t="n">
-        <v>18.44172876304024</v>
+        <v>14.62354694485842</v>
       </c>
       <c r="FT5" t="n">
-        <v>37.65186289120717</v>
+        <v>33.5946348733234</v>
       </c>
       <c r="FU5" t="n">
-        <v>137.1603576751118</v>
+        <v>122.9168405365127</v>
       </c>
       <c r="FV5" t="n">
-        <v>860.9982116244413</v>
+        <v>782.1621460506707</v>
       </c>
       <c r="FW5" t="n">
-        <v>658.1391952309988</v>
+        <v>596.7988077496274</v>
       </c>
       <c r="FX5" t="n">
-        <v>146.0738599105813</v>
+        <v>150.3853949329359</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.2063857999923574</v>
+        <v>0.4492917465048613</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.5800206698418325</v>
+        <v>0.6502008374139521</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.1247334711592693</v>
+        <v>0.1149762904755453</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.5943947704581873</v>
+        <v>0.7281831730117871</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.08039263116051043</v>
+        <v>0.08237083311010321</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.3136208231624371</v>
+        <v>0.3156710789687083</v>
       </c>
       <c r="GE5" t="n">
-        <v>1.460738599105813</v>
+        <v>1.503853949329359</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.9440640848078552</v>
+        <v>0.80373847021388</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.1200990121838091</v>
+        <v>0.06990100679663323</v>
       </c>
       <c r="GH5" t="n">
-        <v>0.9538660091160824</v>
+        <v>0.8151565702315462</v>
       </c>
       <c r="GI5" t="n">
-        <v>0.9578505752263785</v>
+        <v>0.8435346193836921</v>
       </c>
       <c r="GJ5" t="n">
-        <v>0.1037660652647331</v>
+        <v>0.09373647053247565</v>
       </c>
       <c r="GK5" t="n">
-        <v>1.47779433681073</v>
+        <v>-0.4202682563338298</v>
       </c>
       <c r="GL5" t="n">
-        <v>6.160655737704914</v>
+        <v>13.56572280178838</v>
       </c>
       <c r="GM5" t="n">
-        <v>1.237257824143068</v>
+        <v>6.080476900149032</v>
       </c>
       <c r="GN5" t="n">
-        <v>4.739791356184767</v>
+        <v>21.71803278688525</v>
       </c>
       <c r="GO5" t="n">
-        <v>4.809836065573762</v>
+        <v>-11.60387481371088</v>
       </c>
       <c r="GP5" t="n">
-        <v>3.221758569299549</v>
+        <v>8.014605067064085</v>
       </c>
       <c r="GQ5" t="n">
-        <v>2.931147540983595</v>
+        <v>-8.163934426229506</v>
       </c>
       <c r="GR5" t="n">
-        <v>143.640536512667</v>
+        <v>331.8214605067066</v>
       </c>
       <c r="GS5" t="n">
-        <v>-7.446795827123708</v>
+        <v>-3.54724292101341</v>
       </c>
       <c r="GT5" t="n">
-        <v>2.879880774962739</v>
+        <v>5.433084947839047</v>
       </c>
       <c r="GU5" t="n">
-        <v>-17.74456035767513</v>
+        <v>-6.036661698956777</v>
       </c>
       <c r="GV5" t="n">
-        <v>-4.364232488822672</v>
+        <v>-21.55081967213115</v>
       </c>
       <c r="GW5" t="n">
-        <v>3.622652757078986</v>
+        <v>1.951117734724292</v>
       </c>
       <c r="GX5" t="n">
-        <v>-5.332041728763043</v>
+        <v>-1.201788375558868</v>
       </c>
       <c r="GY5" t="n">
-        <v>0.2205663189269629</v>
+        <v>-6.397913561847986</v>
       </c>
       <c r="GZ5" t="n">
-        <v>-1.208047690014951</v>
+        <v>-26.84530551415799</v>
       </c>
       <c r="HA5" t="n">
-        <v>110.5752608047687</v>
+        <v>335.7290611028317</v>
       </c>
       <c r="HB5" t="n">
-        <v>99.79493293591622</v>
+        <v>387.9344262295084</v>
       </c>
       <c r="HC5" t="n">
-        <v>41.83165424739192</v>
+        <v>2.552011922503738</v>
       </c>
       <c r="HD5" t="n">
-        <v>0.06751079521571321</v>
+        <v>-0.2549628593842672</v>
       </c>
       <c r="HE5" t="n">
-        <v>0.08272609159345345</v>
+        <v>0.01147097678920261</v>
       </c>
       <c r="HF5" t="n">
-        <v>0.1315258432967664</v>
+        <v>-0.05967664724743711</v>
       </c>
       <c r="HG5" t="n">
-        <v>0.1204338435507545</v>
+        <v>-0.3464372487919434</v>
       </c>
       <c r="HH5" t="n">
-        <v>0.02210031290885915</v>
+        <v>-0.04191273151968589</v>
       </c>
       <c r="HI5" t="n">
-        <v>0.04133813490721477</v>
+        <v>-0.1353477288973423</v>
       </c>
       <c r="HJ5" t="n">
-        <v>0.418316542473919</v>
+        <v>0.02552011922503739</v>
       </c>
       <c r="HK5" t="n">
-        <v>0.2854645875176811</v>
+        <v>0.1490301493492517</v>
       </c>
       <c r="HL5" t="n">
-        <v>-0.03422177146039135</v>
+        <v>0.02722746265248113</v>
       </c>
       <c r="HM5" t="n">
-        <v>0.04110851553890538</v>
+        <v>0.2144752404622914</v>
       </c>
       <c r="HN5" t="n">
-        <v>0.07146021531951086</v>
+        <v>0.1675905550379346</v>
       </c>
       <c r="HO5" t="n">
-        <v>0.03090722918934549</v>
+        <v>-0.03389962779211656</v>
       </c>
     </row>
     <row r="6">
@@ -3788,31 +4234,31 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -3824,43 +4270,43 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -3869,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>1</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
         <v>1</v>
@@ -3911,25 +4357,25 @@
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
         <v>1</v>
@@ -3938,157 +4384,157 @@
         <v>1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA6" t="n">
         <v>1</v>
       </c>
       <c r="BB6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH6" t="n">
         <v>1</v>
       </c>
       <c r="BI6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
         <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>3.152011922503726</v>
+        <v>2.026825633383011</v>
       </c>
       <c r="BN6" t="n">
-        <v>3.934426229508197</v>
+        <v>2.427719821162444</v>
       </c>
       <c r="BO6" t="n">
-        <v>29.32935916542474</v>
+        <v>19.42175856929955</v>
       </c>
       <c r="BP6" t="n">
-        <v>13.59165424739195</v>
+        <v>4.855439642324888</v>
       </c>
       <c r="BQ6" t="n">
-        <v>99.7913561847988</v>
+        <v>115.5594634873323</v>
       </c>
       <c r="BR6" t="n">
-        <v>23.24888226527571</v>
+        <v>27.19046199701937</v>
       </c>
       <c r="BS6" t="n">
-        <v>12.16095380029806</v>
+        <v>12.62414307004471</v>
       </c>
       <c r="BT6" t="n">
-        <v>38.27123695976155</v>
+        <v>40.30014903129658</v>
       </c>
       <c r="BU6" t="n">
-        <v>1238.628912071535</v>
+        <v>1302.228912071535</v>
       </c>
       <c r="BV6" t="n">
-        <v>30.40238450074516</v>
+        <v>37.38688524590164</v>
       </c>
       <c r="BW6" t="n">
-        <v>13.23397913561848</v>
+        <v>13.1096870342772</v>
       </c>
       <c r="BX6" t="n">
-        <v>20.7451564828614</v>
+        <v>25.24828614008942</v>
       </c>
       <c r="BY6" t="n">
-        <v>27.89865871833085</v>
+        <v>60.20745156482861</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.219076005961252</v>
+        <v>4.3698956780924</v>
       </c>
       <c r="CA6" t="n">
-        <v>11.08792846497765</v>
+        <v>25.24828614008942</v>
       </c>
       <c r="CB6" t="n">
-        <v>28.6140089418778</v>
+        <v>52.4387481371088</v>
       </c>
       <c r="CC6" t="n">
-        <v>101.2220566318927</v>
+        <v>149.061997019374</v>
       </c>
       <c r="CD6" t="n">
-        <v>1060.864381520119</v>
+        <v>1059.942473919523</v>
       </c>
       <c r="CE6" t="n">
-        <v>895.618479880775</v>
+        <v>835.1356184798807</v>
       </c>
       <c r="CF6" t="n">
-        <v>150.8315946348733</v>
+        <v>188.8280476900149</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.2220385309255024</v>
+        <v>0.2890142644241004</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.8073272715205416</v>
+        <v>0.8034596550989993</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.258320914058619</v>
+        <v>0.2237637362637363</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.7948335817188277</v>
+        <v>0.6186117905939068</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.06450729982231221</v>
+        <v>0.09552962972051181</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.1695991868771881</v>
+        <v>0.3609166321762891</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.508315946348733</v>
+        <v>1.888280476900149</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.911496612647069</v>
+        <v>1.313413400310569</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.09498801077666207</v>
+        <v>0.1045541564355765</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.00010878124757</v>
+        <v>1.152191116891466</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.9748094662448145</v>
+        <v>1.146268509810847</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.08528851837042691</v>
+        <v>0.1258558093944848</v>
       </c>
       <c r="CS6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
         <v>1</v>
       </c>
       <c r="CU6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CW6" t="n">
         <v>1</v>
       </c>
       <c r="CX6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CY6" t="n">
         <v>0</v>
@@ -4097,13 +4543,13 @@
         <v>1</v>
       </c>
       <c r="DA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DB6" t="n">
         <v>0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD6" t="n">
         <v>0</v>
@@ -4115,7 +4561,7 @@
         <v>1</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DH6" t="n">
         <v>0</v>
@@ -4124,55 +4570,55 @@
         <v>1</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
       </c>
       <c r="DL6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DM6" t="n">
         <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DP6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR6" t="n">
         <v>0</v>
       </c>
       <c r="DS6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT6" t="n">
         <v>0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EA6" t="n">
         <v>0</v>
@@ -4181,10 +4627,10 @@
         <v>1</v>
       </c>
       <c r="EC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ED6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>1</v>
@@ -4193,22 +4639,22 @@
         <v>1</v>
       </c>
       <c r="EG6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EJ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK6" t="n">
         <v>0</v>
       </c>
       <c r="EL6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EM6" t="n">
         <v>1</v>
@@ -4220,37 +4666,37 @@
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EQ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ES6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ET6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
         <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FA6" t="n">
         <v>0</v>
@@ -4259,199 +4705,199 @@
         <v>1</v>
       </c>
       <c r="FC6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FD6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
-        <v>2.86140089418778</v>
+        <v>2.943368107302534</v>
       </c>
       <c r="FF6" t="n">
-        <v>6.28166915052161</v>
+        <v>2.85424739195231</v>
       </c>
       <c r="FG6" t="n">
-        <v>29.73323397913562</v>
+        <v>28.06676602086439</v>
       </c>
       <c r="FH6" t="n">
-        <v>12.56333830104322</v>
+        <v>7.135618479880775</v>
       </c>
       <c r="FI6" t="n">
-        <v>100.0879284649776</v>
+        <v>104.1800298062593</v>
       </c>
       <c r="FJ6" t="n">
-        <v>18.00745156482861</v>
+        <v>35.67809239940387</v>
       </c>
       <c r="FK6" t="n">
-        <v>12.14456035767511</v>
+        <v>14.74694485842027</v>
       </c>
       <c r="FL6" t="n">
-        <v>33.08345752608048</v>
+        <v>49.94932935916543</v>
       </c>
       <c r="FM6" t="n">
-        <v>1307.424739195231</v>
+        <v>1252.063189269747</v>
       </c>
       <c r="FN6" t="n">
-        <v>36.43368107302533</v>
+        <v>33.775260804769</v>
       </c>
       <c r="FO6" t="n">
-        <v>19.68256333830104</v>
+        <v>19.02831594634873</v>
       </c>
       <c r="FP6" t="n">
-        <v>16.75111773472429</v>
+        <v>25.21251862891207</v>
       </c>
       <c r="FQ6" t="n">
-        <v>38.94634873323398</v>
+        <v>44.71654247391952</v>
       </c>
       <c r="FR6" t="n">
-        <v>1.675111773472429</v>
+        <v>4.757078986587183</v>
       </c>
       <c r="FS6" t="n">
-        <v>17.58867362146051</v>
+        <v>11.89269746646796</v>
       </c>
       <c r="FT6" t="n">
-        <v>36.01490312965723</v>
+        <v>43.28941877794337</v>
       </c>
       <c r="FU6" t="n">
-        <v>104.6944858420268</v>
+        <v>137.4795827123696</v>
       </c>
       <c r="FV6" t="n">
-        <v>1087.147540983607</v>
+        <v>981.8611028315947</v>
       </c>
       <c r="FW6" t="n">
-        <v>930.9433681073026</v>
+        <v>754.948435171386</v>
       </c>
       <c r="FX6" t="n">
-        <v>177.0593144560357</v>
+        <v>181.8155588673621</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.5151231095622812</v>
+        <v>0.2207772555313539</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.9026029118997196</v>
+        <v>0.5779647674729643</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.1260439496215774</v>
+        <v>0.3699950322901142</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.8701959323222584</v>
+        <v>0.779632389468455</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.06102298811306488</v>
+        <v>0.1196739944073191</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.2206992731527079</v>
+        <v>0.3497736278196966</v>
       </c>
       <c r="GE6" t="n">
-        <v>1.770593144560358</v>
+        <v>1.818155588673621</v>
       </c>
       <c r="GF6" t="n">
-        <v>1.310911406683624</v>
+        <v>1.174417417222834</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.1011587418236878</v>
+        <v>0.1063655946375677</v>
       </c>
       <c r="GH6" t="n">
-        <v>0.9972515769817845</v>
+        <v>1.0376386115561</v>
       </c>
       <c r="GI6" t="n">
-        <v>1.011270038757607</v>
+        <v>1.05694818402794</v>
       </c>
       <c r="GJ6" t="n">
-        <v>0.08370380427605432</v>
+        <v>0.1535391291832646</v>
       </c>
       <c r="GK6" t="n">
-        <v>-2.347242921013413</v>
+        <v>-0.4265275707898661</v>
       </c>
       <c r="GL6" t="n">
-        <v>-0.4038748137108819</v>
+        <v>-8.645007451564833</v>
       </c>
       <c r="GM6" t="n">
-        <v>1.028315946348732</v>
+        <v>-2.280178837555887</v>
       </c>
       <c r="GN6" t="n">
-        <v>-0.296572280178836</v>
+        <v>11.37943368107302</v>
       </c>
       <c r="GO6" t="n">
-        <v>5.241430700447093</v>
+        <v>-8.4876304023845</v>
       </c>
       <c r="GP6" t="n">
-        <v>0.01639344262295239</v>
+        <v>-2.122801788375559</v>
       </c>
       <c r="GQ6" t="n">
-        <v>5.187779433681072</v>
+        <v>-9.649180327868848</v>
       </c>
       <c r="GR6" t="n">
-        <v>-68.79582712369597</v>
+        <v>50.16572280178843</v>
       </c>
       <c r="GS6" t="n">
-        <v>-6.031296572280176</v>
+        <v>3.611624441132641</v>
       </c>
       <c r="GT6" t="n">
-        <v>-6.448584202682563</v>
+        <v>-5.918628912071535</v>
       </c>
       <c r="GU6" t="n">
-        <v>3.994038748137108</v>
+        <v>0.03576751117734744</v>
       </c>
       <c r="GV6" t="n">
-        <v>-11.04769001490313</v>
+        <v>15.49090909090908</v>
       </c>
       <c r="GW6" t="n">
-        <v>1.543964232488823</v>
+        <v>-0.3871833084947838</v>
       </c>
       <c r="GX6" t="n">
-        <v>-6.500745156482862</v>
+        <v>13.35558867362146</v>
       </c>
       <c r="GY6" t="n">
-        <v>-7.400894187779432</v>
+        <v>9.149329359165428</v>
       </c>
       <c r="GZ6" t="n">
-        <v>-3.472429210134138</v>
+        <v>11.58241430700446</v>
       </c>
       <c r="HA6" t="n">
-        <v>-26.28315946348721</v>
+        <v>78.08137108792835</v>
       </c>
       <c r="HB6" t="n">
-        <v>-35.32488822652761</v>
+        <v>80.1871833084947</v>
       </c>
       <c r="HC6" t="n">
-        <v>-26.2277198211624</v>
+        <v>7.012488822652784</v>
       </c>
       <c r="HD6" t="n">
-        <v>-0.2930845786367788</v>
+        <v>0.06823700889274656</v>
       </c>
       <c r="HE6" t="n">
-        <v>-0.09527564037917802</v>
+        <v>0.225494887626035</v>
       </c>
       <c r="HF6" t="n">
-        <v>0.1322769644370415</v>
+        <v>-0.1462312960263779</v>
       </c>
       <c r="HG6" t="n">
-        <v>-0.07536235060343077</v>
+        <v>-0.1610205988745482</v>
       </c>
       <c r="HH6" t="n">
-        <v>0.003484311709247331</v>
+        <v>-0.02414436468680732</v>
       </c>
       <c r="HI6" t="n">
-        <v>-0.05110008627551985</v>
+        <v>0.01114300435659249</v>
       </c>
       <c r="HJ6" t="n">
-        <v>-0.2622771982116243</v>
+        <v>0.07012488822652796</v>
       </c>
       <c r="HK6" t="n">
-        <v>-0.3994147940365552</v>
+        <v>0.1389959830877345</v>
       </c>
       <c r="HL6" t="n">
-        <v>-0.006170731047025702</v>
+        <v>-0.001811438201991145</v>
       </c>
       <c r="HM6" t="n">
-        <v>0.002857204265785729</v>
+        <v>0.1145525053353658</v>
       </c>
       <c r="HN6" t="n">
-        <v>-0.036460572512793</v>
+        <v>0.08932032578290716</v>
       </c>
       <c r="HO6" t="n">
-        <v>0.00158471409437258</v>
+        <v>-0.02768331978877978</v>
       </c>
     </row>
     <row r="7">
@@ -4459,16 +4905,16 @@
         <v>1</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -4477,19 +4923,19 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
@@ -4498,13 +4944,13 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -4516,7 +4962,7 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>1</v>
@@ -4525,10 +4971,10 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -4537,16 +4983,16 @@
         <v>1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -4555,34 +5001,34 @@
         <v>1</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>1</v>
       </c>
       <c r="AP7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
         <v>1</v>
@@ -4597,25 +5043,25 @@
         <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
         <v>1</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA7" t="n">
         <v>1</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC7" t="n">
         <v>1</v>
@@ -4624,13 +5070,13 @@
         <v>1</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF7" t="n">
         <v>1</v>
       </c>
       <c r="BG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH7" t="n">
         <v>1</v>
@@ -4639,490 +5085,490 @@
         <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM7" t="n">
+        <v>1.974664679582712</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1.949329359165425</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>38.49925484351714</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>11.69597615499255</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>136.4530551415797</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>30.21460506706409</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>17.54396423248883</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>51.65722801788376</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1546.305514157973</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>41.91058122205663</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>24.85394932935917</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>25.34128166915053</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>41.91058122205663</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>9.259314456035769</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>21.44262295081968</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>49.22056631892698</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>190.0596125186289</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>1264.627421758569</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>1020.961251862891</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>195.2740685543965</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.1380774962742176</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.7206438849234365</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.2709511551538378</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.8072276953051917</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.0995749142594976</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0.3775900286246035</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>1.952740685543964</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0.9315272721445503</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0.1661470943475344</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>1.361757096753157</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>1.324934522752482</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0.1348187268317759</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>1</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
         <v>1.982116244411326</v>
       </c>
-      <c r="BN7" t="n">
-        <v>2.083457526080477</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>24.16810730253353</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>8.333830104321908</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>122.9239940387481</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>25.41818181818182</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>12.50074515648286</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>35.83546944858421</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>1475.087928464978</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>35.41877794336811</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>14.16751117734724</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>13.33412816691505</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>42.91922503725783</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>3.750223546944859</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>12.08405365126677</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>38.75230998509688</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>120.0071535022355</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>1272.575856929955</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>1090.898360655738</v>
-      </c>
-      <c r="CF7" t="n">
-        <v>178.3022950819672</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>0.1790781349797743</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>0.6722081793020691</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>0.2991249733872685</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>0.5491398765169258</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>0.05993357162516338</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>0.2002042306292797</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>1.783022950819672</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>0.9682735297489397</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>0.1267091494020998</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>1.233930915792427</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>1.187598218718039</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>0.08162432886860764</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CT7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DA7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DY7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DZ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="EA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB7" t="n">
-        <v>1</v>
-      </c>
-      <c r="EC7" t="n">
-        <v>1</v>
-      </c>
-      <c r="ED7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF7" t="n">
-        <v>1</v>
-      </c>
-      <c r="EG7" t="n">
-        <v>1</v>
-      </c>
-      <c r="EH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EI7" t="n">
-        <v>1</v>
-      </c>
-      <c r="EJ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="EK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EL7" t="n">
-        <v>1</v>
-      </c>
-      <c r="EM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EO7" t="n">
-        <v>1</v>
-      </c>
-      <c r="EP7" t="n">
-        <v>1</v>
-      </c>
-      <c r="EQ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="ER7" t="n">
-        <v>1</v>
-      </c>
-      <c r="ES7" t="n">
-        <v>0</v>
-      </c>
-      <c r="ET7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EU7" t="n">
-        <v>1</v>
-      </c>
-      <c r="EV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EZ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="FA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="FB7" t="n">
-        <v>1</v>
-      </c>
-      <c r="FC7" t="n">
-        <v>1</v>
-      </c>
-      <c r="FD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="FE7" t="n">
-        <v>1.445603576751118</v>
-      </c>
       <c r="FF7" t="n">
-        <v>1.385096870342772</v>
+        <v>1.621460506706409</v>
       </c>
       <c r="FG7" t="n">
-        <v>19.85305514157973</v>
+        <v>25.53800298062593</v>
       </c>
       <c r="FH7" t="n">
-        <v>6.92548435171386</v>
+        <v>7.296572280178839</v>
       </c>
       <c r="FI7" t="n">
-        <v>111.2694485842027</v>
+        <v>117.150521609538</v>
       </c>
       <c r="FJ7" t="n">
-        <v>20.31475409836066</v>
+        <v>23.51117734724292</v>
       </c>
       <c r="FK7" t="n">
-        <v>7.848882265275708</v>
+        <v>13.78241430700447</v>
       </c>
       <c r="FL7" t="n">
-        <v>39.70611028315946</v>
+        <v>37.29359165424739</v>
       </c>
       <c r="FM7" t="n">
-        <v>1309.3782414307</v>
+        <v>1457.287630402385</v>
       </c>
       <c r="FN7" t="n">
-        <v>39.70611028315946</v>
+        <v>34.45603576751118</v>
       </c>
       <c r="FO7" t="n">
-        <v>15.23606557377049</v>
+        <v>12.56631892697467</v>
       </c>
       <c r="FP7" t="n">
-        <v>20.31475409836066</v>
+        <v>14.18777943368107</v>
       </c>
       <c r="FQ7" t="n">
-        <v>52.63368107302534</v>
+        <v>42.15797317436662</v>
       </c>
       <c r="FR7" t="n">
-        <v>3.693591654247392</v>
+        <v>3.242921013412817</v>
       </c>
       <c r="FS7" t="n">
-        <v>17.08286140089419</v>
+        <v>12.56631892697467</v>
       </c>
       <c r="FT7" t="n">
-        <v>40.16780923994038</v>
+        <v>35.67213114754099</v>
       </c>
       <c r="FU7" t="n">
-        <v>135.7394932935916</v>
+        <v>111.070044709389</v>
       </c>
       <c r="FV7" t="n">
-        <v>1068.833084947839</v>
+        <v>1258.253353204173</v>
       </c>
       <c r="FW7" t="n">
-        <v>878.1514157973173</v>
+        <v>1083.540983606558</v>
       </c>
       <c r="FX7" t="n">
-        <v>189.2965722801788</v>
+        <v>174.185394932936</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.1685567619993849</v>
+        <v>0.1404300617415372</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.9193672083836018</v>
+        <v>0.5593512299920647</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.4810053966740765</v>
+        <v>0.2546153300251661</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.8696710019919683</v>
+        <v>0.716107935780067</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.08491153129439102</v>
+        <v>0.06087438250521106</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.2961591048965299</v>
+        <v>0.1832841691114603</v>
       </c>
       <c r="GE7" t="n">
-        <v>1.892965722801788</v>
+        <v>1.741853949329359</v>
       </c>
       <c r="GF7" t="n">
-        <v>1.04898941078632</v>
+        <v>0.9455735521309293</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.1101064749341317</v>
+        <v>0.1122309206270288</v>
       </c>
       <c r="GH7" t="n">
-        <v>1.113731267176925</v>
+        <v>1.177418670409445</v>
       </c>
       <c r="GI7" t="n">
-        <v>1.103911887628435</v>
+        <v>1.135261523279687</v>
       </c>
       <c r="GJ7" t="n">
-        <v>0.1014289357111451</v>
+        <v>0.08406046167554942</v>
       </c>
       <c r="GK7" t="n">
-        <v>0.6983606557377051</v>
+        <v>0.3278688524590165</v>
       </c>
       <c r="GL7" t="n">
-        <v>4.315052160953801</v>
+        <v>12.96125186289121</v>
       </c>
       <c r="GM7" t="n">
-        <v>1.408345752608049</v>
+        <v>4.399403874813712</v>
       </c>
       <c r="GN7" t="n">
-        <v>11.65454545454546</v>
+        <v>19.30253353204174</v>
       </c>
       <c r="GO7" t="n">
-        <v>5.103427719821163</v>
+        <v>6.703427719821168</v>
       </c>
       <c r="GP7" t="n">
-        <v>4.651862891207155</v>
+        <v>3.761549925484355</v>
       </c>
       <c r="GQ7" t="n">
-        <v>-3.870640834575255</v>
+        <v>14.36363636363637</v>
       </c>
       <c r="GR7" t="n">
-        <v>165.7096870342773</v>
+        <v>89.01788375558885</v>
       </c>
       <c r="GS7" t="n">
-        <v>-4.287332339791348</v>
+        <v>7.454545454545453</v>
       </c>
       <c r="GT7" t="n">
-        <v>-1.068554396423247</v>
+        <v>12.2876304023845</v>
       </c>
       <c r="GU7" t="n">
-        <v>-6.980625931445601</v>
+        <v>11.15350223546945</v>
       </c>
       <c r="GV7" t="n">
-        <v>-9.714456035767505</v>
+        <v>-0.2473919523099894</v>
       </c>
       <c r="GW7" t="n">
-        <v>0.05663189269746693</v>
+        <v>6.016393442622952</v>
       </c>
       <c r="GX7" t="n">
-        <v>-4.998807749627423</v>
+        <v>8.876304023845009</v>
       </c>
       <c r="GY7" t="n">
-        <v>-1.415499254843503</v>
+        <v>13.548435171386</v>
       </c>
       <c r="GZ7" t="n">
-        <v>-15.73233979135615</v>
+        <v>78.98956780923996</v>
       </c>
       <c r="HA7" t="n">
-        <v>203.7427719821162</v>
+        <v>6.374068554396445</v>
       </c>
       <c r="HB7" t="n">
-        <v>212.7469448584205</v>
+        <v>-62.57973174366623</v>
       </c>
       <c r="HC7" t="n">
-        <v>-10.99427719821159</v>
+        <v>21.08867362146049</v>
       </c>
       <c r="HD7" t="n">
-        <v>0.01052137298038935</v>
+        <v>-0.002352565467319573</v>
       </c>
       <c r="HE7" t="n">
-        <v>-0.2471590290815326</v>
+        <v>0.1612926549313718</v>
       </c>
       <c r="HF7" t="n">
-        <v>-0.181880423286808</v>
+        <v>0.01633582512867165</v>
       </c>
       <c r="HG7" t="n">
-        <v>-0.3205311254750426</v>
+        <v>0.09111975952512463</v>
       </c>
       <c r="HH7" t="n">
-        <v>-0.02497795966922765</v>
+        <v>0.03870053175428655</v>
       </c>
       <c r="HI7" t="n">
-        <v>-0.09595487426725019</v>
+        <v>0.1943058595131432</v>
       </c>
       <c r="HJ7" t="n">
-        <v>-0.109942771982116</v>
+        <v>0.210886736214605</v>
       </c>
       <c r="HK7" t="n">
-        <v>-0.08071588103737992</v>
+        <v>-0.01404627998637897</v>
       </c>
       <c r="HL7" t="n">
-        <v>0.01660267446796819</v>
+        <v>0.05391617372050557</v>
       </c>
       <c r="HM7" t="n">
-        <v>0.1201996486155015</v>
+        <v>0.184338426343712</v>
       </c>
       <c r="HN7" t="n">
-        <v>0.08368633108960366</v>
+        <v>0.1896729994727953</v>
       </c>
       <c r="HO7" t="n">
-        <v>-0.01980460684253743</v>
+        <v>0.05075826515622647</v>
       </c>
     </row>
     <row r="8">
@@ -5133,34 +5579,34 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>1</v>
@@ -5169,22 +5615,22 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>1</v>
@@ -5193,34 +5639,34 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -5229,28 +5675,28 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="n">
         <v>1</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ8" t="n">
         <v>1</v>
@@ -5259,34 +5705,34 @@
         <v>1</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT8" t="n">
         <v>1</v>
       </c>
       <c r="AU8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
         <v>1</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
         <v>1</v>
@@ -5295,13 +5741,13 @@
         <v>1</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH8" t="n">
         <v>1</v>
@@ -5316,109 +5762,109 @@
         <v>1</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.363636363636364</v>
+        <v>1.669150521609538</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.104321907600597</v>
+        <v>2.205663189269747</v>
       </c>
       <c r="BO8" t="n">
-        <v>22.16333830104323</v>
+        <v>30.87928464977645</v>
       </c>
       <c r="BP8" t="n">
-        <v>7.798211624441134</v>
+        <v>10.4769001490313</v>
       </c>
       <c r="BQ8" t="n">
-        <v>81.26557377049183</v>
+        <v>124.6199701937407</v>
       </c>
       <c r="BR8" t="n">
-        <v>29.14068554396424</v>
+        <v>31.43070044709389</v>
       </c>
       <c r="BS8" t="n">
-        <v>3.693889716840538</v>
+        <v>12.13114754098361</v>
       </c>
       <c r="BT8" t="n">
-        <v>19.70074515648286</v>
+        <v>48.52459016393443</v>
       </c>
       <c r="BU8" t="n">
-        <v>940.7105812220568</v>
+        <v>1445.812220566319</v>
       </c>
       <c r="BV8" t="n">
-        <v>37.34932935916543</v>
+        <v>39.150521609538</v>
       </c>
       <c r="BW8" t="n">
-        <v>14.36512667660209</v>
+        <v>14.88822652757079</v>
       </c>
       <c r="BX8" t="n">
-        <v>22.98420268256334</v>
+        <v>33.0849478390462</v>
       </c>
       <c r="BY8" t="n">
-        <v>63.61698956780926</v>
+        <v>54.0387481371088</v>
       </c>
       <c r="BZ8" t="n">
-        <v>4.925186289120716</v>
+        <v>4.96274217585693</v>
       </c>
       <c r="CA8" t="n">
-        <v>23.3946348733234</v>
+        <v>26.46795827123696</v>
       </c>
       <c r="CB8" t="n">
-        <v>35.70760059612519</v>
+        <v>43.5618479880775</v>
       </c>
       <c r="CC8" t="n">
-        <v>132.9800298062593</v>
+        <v>199.0611028315946</v>
       </c>
       <c r="CD8" t="n">
-        <v>704.3016393442624</v>
+        <v>1159.076005961252</v>
       </c>
       <c r="CE8" t="n">
-        <v>524.1219076005963</v>
+        <v>908.1818181818181</v>
       </c>
       <c r="CF8" t="n">
-        <v>148.7816691505217</v>
+        <v>212.6259314456036</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.3752522886949117</v>
+        <v>0.1573484472143191</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.7604544486809763</v>
+        <v>0.8535805145343148</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.2673948182964577</v>
+        <v>0.4095073200666258</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.6919904276051818</v>
+        <v>0.8499491864969203</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.05941831873020619</v>
+        <v>0.1112515171830125</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.4203195883142173</v>
+        <v>0.5050386060698052</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.487816691505216</v>
+        <v>2.126259314456036</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.852935232719732</v>
+        <v>1.290157400385769</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.09856396636925348</v>
+        <v>0.1142541961249179</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.8151078430959925</v>
+        <v>1.249468963888558</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.8656858221661677</v>
+        <v>1.267075600561387</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.06907088581916618</v>
+        <v>0.1396702147962199</v>
       </c>
       <c r="CS8" t="n">
         <v>1</v>
       </c>
       <c r="CT8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CU8" t="n">
         <v>1</v>
@@ -5430,7 +5876,7 @@
         <v>1</v>
       </c>
       <c r="CX8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
         <v>1</v>
@@ -5439,46 +5885,46 @@
         <v>1</v>
       </c>
       <c r="DA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DB8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC8" t="n">
         <v>1</v>
       </c>
       <c r="DD8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DF8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DG8" t="n">
         <v>1</v>
       </c>
       <c r="DH8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DI8" t="n">
         <v>1</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DK8" t="n">
         <v>1</v>
       </c>
       <c r="DL8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DM8" t="n">
         <v>0</v>
       </c>
       <c r="DN8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
         <v>1</v>
@@ -5496,13 +5942,13 @@
         <v>0</v>
       </c>
       <c r="DT8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU8" t="n">
         <v>1</v>
       </c>
       <c r="DV8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
@@ -5514,7 +5960,7 @@
         <v>1</v>
       </c>
       <c r="DZ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EA8" t="n">
         <v>0</v>
@@ -5532,13 +5978,13 @@
         <v>0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EG8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EH8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
         <v>0</v>
@@ -5550,7 +5996,7 @@
         <v>1</v>
       </c>
       <c r="EL8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
         <v>0</v>
@@ -5562,37 +6008,37 @@
         <v>1</v>
       </c>
       <c r="EP8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EQ8" t="n">
         <v>1</v>
       </c>
       <c r="ER8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ET8" t="n">
         <v>1</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EV8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EW8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EY8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FA8" t="n">
         <v>1</v>
@@ -5604,207 +6050,207 @@
         <v>1</v>
       </c>
       <c r="FD8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FE8" t="n">
-        <v>2.429210134128167</v>
+        <v>3.152011922503726</v>
       </c>
       <c r="FF8" t="n">
-        <v>2.035767511177347</v>
+        <v>3.374664679582712</v>
       </c>
       <c r="FG8" t="n">
-        <v>23.61490312965723</v>
+        <v>26.24739195230999</v>
       </c>
       <c r="FH8" t="n">
-        <v>6.514456035767513</v>
+        <v>11.24888226527571</v>
       </c>
       <c r="FI8" t="n">
-        <v>94.05245901639346</v>
+        <v>110.2390461997019</v>
       </c>
       <c r="FJ8" t="n">
-        <v>20.76482861400894</v>
+        <v>24.3725782414307</v>
       </c>
       <c r="FK8" t="n">
-        <v>7.73591654247392</v>
+        <v>13.12369597615499</v>
       </c>
       <c r="FL8" t="n">
-        <v>25.24351713859911</v>
+        <v>40.12101341281669</v>
       </c>
       <c r="FM8" t="n">
-        <v>1236.118032786885</v>
+        <v>1341.616691505216</v>
       </c>
       <c r="FN8" t="n">
-        <v>34.60804769001491</v>
+        <v>30.37198211624441</v>
       </c>
       <c r="FO8" t="n">
-        <v>20.35767511177347</v>
+        <v>12.37377049180328</v>
       </c>
       <c r="FP8" t="n">
-        <v>21.98628912071536</v>
+        <v>23.99761549925485</v>
       </c>
       <c r="FQ8" t="n">
-        <v>54.96572280178838</v>
+        <v>29.24709388971684</v>
       </c>
       <c r="FR8" t="n">
-        <v>4.478688524590165</v>
+        <v>2.999701937406856</v>
       </c>
       <c r="FS8" t="n">
-        <v>13.84321907600596</v>
+        <v>13.12369597615499</v>
       </c>
       <c r="FT8" t="n">
-        <v>31.35081967213115</v>
+        <v>28.87213114754098</v>
       </c>
       <c r="FU8" t="n">
-        <v>118.0745156482862</v>
+        <v>114.3636363636364</v>
       </c>
       <c r="FV8" t="n">
-        <v>1005.261997019374</v>
+        <v>1164.259314456036</v>
       </c>
       <c r="FW8" t="n">
-        <v>844.8435171385992</v>
+        <v>994.0262295081968</v>
       </c>
       <c r="FX8" t="n">
-        <v>170.1494485842027</v>
+        <v>159.9216095380029</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.1918630094859603</v>
+        <v>0.2515185303623612</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.5279262176803161</v>
+        <v>0.7807296097632594</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.1964677217136234</v>
+        <v>0.2395595297234641</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.7195395298524958</v>
+        <v>0.6613926146713032</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.05165061774177715</v>
+        <v>0.06502165788097551</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.2426061704964196</v>
+        <v>0.1839201473970516</v>
       </c>
       <c r="GE8" t="n">
-        <v>1.701494485842027</v>
+        <v>1.59921609538003</v>
       </c>
       <c r="GF8" t="n">
-        <v>1.040344527571897</v>
+        <v>0.9466245979208237</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.09870757393263246</v>
+        <v>0.09919544268966173</v>
       </c>
       <c r="GH8" t="n">
-        <v>0.9429210256303971</v>
+        <v>1.105560763935648</v>
       </c>
       <c r="GI8" t="n">
-        <v>0.9650812785371901</v>
+        <v>1.069260814074806</v>
       </c>
       <c r="GJ8" t="n">
-        <v>0.0675562595734614</v>
+        <v>0.08630599428231797</v>
       </c>
       <c r="GK8" t="n">
-        <v>2.06855439642325</v>
+        <v>-1.169001490312966</v>
       </c>
       <c r="GL8" t="n">
-        <v>-1.451564828614003</v>
+        <v>4.631892697466466</v>
       </c>
       <c r="GM8" t="n">
-        <v>1.283755588673621</v>
+        <v>-0.7719821162444109</v>
       </c>
       <c r="GN8" t="n">
-        <v>-12.78688524590163</v>
+        <v>14.38092399403877</v>
       </c>
       <c r="GO8" t="n">
-        <v>8.375856929955297</v>
+        <v>7.058122205663192</v>
       </c>
       <c r="GP8" t="n">
-        <v>-4.042026825633382</v>
+        <v>-0.9925484351713845</v>
       </c>
       <c r="GQ8" t="n">
-        <v>-5.542771982116246</v>
+        <v>8.403576751117747</v>
       </c>
       <c r="GR8" t="n">
-        <v>-295.4074515648285</v>
+        <v>104.1955290611029</v>
       </c>
       <c r="GS8" t="n">
-        <v>2.741281669150524</v>
+        <v>8.778539493293593</v>
       </c>
       <c r="GT8" t="n">
-        <v>-5.992548435171384</v>
+        <v>2.514456035767514</v>
       </c>
       <c r="GU8" t="n">
-        <v>0.9979135618479873</v>
+        <v>9.087332339791356</v>
       </c>
       <c r="GV8" t="n">
-        <v>8.651266766020875</v>
+        <v>24.79165424739196</v>
       </c>
       <c r="GW8" t="n">
-        <v>0.4464977645305508</v>
+        <v>1.963040238450075</v>
       </c>
       <c r="GX8" t="n">
-        <v>9.551415797317443</v>
+        <v>13.34426229508197</v>
       </c>
       <c r="GY8" t="n">
-        <v>4.356780923994037</v>
+        <v>14.68971684053652</v>
       </c>
       <c r="GZ8" t="n">
-        <v>14.90551415797317</v>
+        <v>84.69746646795828</v>
       </c>
       <c r="HA8" t="n">
-        <v>-300.9603576751118</v>
+        <v>-5.183308494783887</v>
       </c>
       <c r="HB8" t="n">
-        <v>-320.7216095380029</v>
+        <v>-85.84441132637869</v>
       </c>
       <c r="HC8" t="n">
-        <v>-21.36777943368105</v>
+        <v>52.70432190760067</v>
       </c>
       <c r="HD8" t="n">
-        <v>0.1833892792089514</v>
+        <v>-0.09417008314804215</v>
       </c>
       <c r="HE8" t="n">
-        <v>0.2325282310006602</v>
+        <v>0.07285090477105538</v>
       </c>
       <c r="HF8" t="n">
-        <v>0.0709270965828343</v>
+        <v>0.1699477903431617</v>
       </c>
       <c r="HG8" t="n">
-        <v>-0.02754910224731399</v>
+        <v>0.1885565718256171</v>
       </c>
       <c r="HH8" t="n">
-        <v>0.007767700988429042</v>
+        <v>0.04622985930203699</v>
       </c>
       <c r="HI8" t="n">
-        <v>0.1777134178177976</v>
+        <v>0.3211184586727536</v>
       </c>
       <c r="HJ8" t="n">
-        <v>-0.2136777943368107</v>
+        <v>0.5270432190760062</v>
       </c>
       <c r="HK8" t="n">
-        <v>-0.1874092948521654</v>
+        <v>0.3435328024649453</v>
       </c>
       <c r="HL8" t="n">
-        <v>-0.0001436075633789863</v>
+        <v>0.01505875343525613</v>
       </c>
       <c r="HM8" t="n">
-        <v>-0.1278131825344047</v>
+        <v>0.1439081999529106</v>
       </c>
       <c r="HN8" t="n">
-        <v>-0.09939545637102232</v>
+        <v>0.1978147864865809</v>
       </c>
       <c r="HO8" t="n">
-        <v>0.001514626245704781</v>
+        <v>0.05336422051390191</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -5816,22 +6262,22 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
@@ -5846,13 +6292,13 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
@@ -5861,19 +6307,19 @@
         <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -5882,22 +6328,22 @@
         <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -5906,19 +6352,19 @@
         <v>1</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5927,31 +6373,31 @@
         <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
         <v>1</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW9" t="n">
         <v>1</v>
       </c>
       <c r="AX9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -5963,16 +6409,16 @@
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
         <v>1</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH9" t="n">
         <v>1</v>
@@ -5984,127 +6430,127 @@
         <v>1</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>2.116244411326379</v>
+        <v>4.008941877794337</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.834873323397914</v>
+        <v>6.385692995529062</v>
       </c>
       <c r="BO9" t="n">
-        <v>28.89925484351714</v>
+        <v>38.71326378539494</v>
       </c>
       <c r="BP9" t="n">
-        <v>6.880774962742176</v>
+        <v>13.17049180327869</v>
       </c>
       <c r="BQ9" t="n">
-        <v>109.6336810730253</v>
+        <v>140.8843517138599</v>
       </c>
       <c r="BR9" t="n">
-        <v>26.14694485842027</v>
+        <v>20.75350223546945</v>
       </c>
       <c r="BS9" t="n">
-        <v>10.550521609538</v>
+        <v>12.77138599105812</v>
       </c>
       <c r="BT9" t="n">
-        <v>48.62414307004471</v>
+        <v>27.53830104321908</v>
       </c>
       <c r="BU9" t="n">
-        <v>1261.475409836066</v>
+        <v>1568.884947839046</v>
       </c>
       <c r="BV9" t="n">
-        <v>32.11028315946348</v>
+        <v>31.13025335320417</v>
       </c>
       <c r="BW9" t="n">
-        <v>16.51385991058122</v>
+        <v>12.77138599105812</v>
       </c>
       <c r="BX9" t="n">
-        <v>38.07362146050671</v>
+        <v>23.54724292101342</v>
       </c>
       <c r="BY9" t="n">
-        <v>61.46825633383011</v>
+        <v>36.7177347242921</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.75230998509687</v>
+        <v>3.991058122205664</v>
       </c>
       <c r="CA9" t="n">
-        <v>20.18360655737705</v>
+        <v>7.982116244411327</v>
       </c>
       <c r="CB9" t="n">
-        <v>43.57824143070044</v>
+        <v>32.32757078986587</v>
       </c>
       <c r="CC9" t="n">
-        <v>166.9734724292101</v>
+        <v>86.60596125186289</v>
       </c>
       <c r="CD9" t="n">
-        <v>1020.18956780924</v>
+        <v>1346.18390461997</v>
       </c>
       <c r="CE9" t="n">
-        <v>796.3350223546945</v>
+        <v>1189.734426229508</v>
       </c>
       <c r="CF9" t="n">
-        <v>178.2579433681073</v>
+        <v>175.2074515648286</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.1101527570789866</v>
+        <v>0.3317741498441946</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.4590201192250372</v>
+        <v>0.625172740821027</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.1081412897613476</v>
+        <v>0.1472890497480661</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.7192641158263146</v>
+        <v>0.7712878196484755</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.1098387576464329</v>
+        <v>0.03926518750757951</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.3821032045854785</v>
+        <v>0.1314995787830815</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.782579433681073</v>
+        <v>1.752074515648286</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.319753867723342</v>
+        <v>1.169031122000351</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.1008554869871452</v>
+        <v>0.1615498521700205</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.100021821302593</v>
+        <v>1.407684665598594</v>
       </c>
       <c r="CQ9" t="n">
-        <v>1.099066398498734</v>
+        <v>1.345370619712768</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.1332413308397898</v>
+        <v>0.05788559589141996</v>
       </c>
       <c r="CS9" t="n">
         <v>1</v>
       </c>
       <c r="CT9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CU9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CW9" t="n">
         <v>0</v>
       </c>
       <c r="CX9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CY9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CZ9" t="n">
         <v>0</v>
@@ -6116,46 +6562,46 @@
         <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>1</v>
       </c>
       <c r="DF9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG9" t="n">
         <v>1</v>
       </c>
       <c r="DH9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DI9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ9" t="n">
         <v>0</v>
       </c>
       <c r="DK9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>1</v>
       </c>
       <c r="DM9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
         <v>0</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ9" t="n">
         <v>0</v>
@@ -6173,13 +6619,13 @@
         <v>1</v>
       </c>
       <c r="DV9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DX9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DY9" t="n">
         <v>1</v>
@@ -6197,34 +6643,34 @@
         <v>1</v>
       </c>
       <c r="ED9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EF9" t="n">
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EJ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK9" t="n">
         <v>0</v>
       </c>
       <c r="EL9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EN9" t="n">
         <v>0</v>
@@ -6257,886 +6703,440 @@
         <v>1</v>
       </c>
       <c r="EX9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EZ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FA9" t="n">
         <v>0</v>
       </c>
       <c r="FB9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FC9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FD9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>1.974664679582712</v>
+        <v>1.72876304023845</v>
       </c>
       <c r="FF9" t="n">
-        <v>2.891803278688525</v>
+        <v>2.526676602086439</v>
       </c>
       <c r="FG9" t="n">
-        <v>32.29180327868853</v>
+        <v>16.60387481371088</v>
       </c>
       <c r="FH9" t="n">
-        <v>9.639344262295083</v>
+        <v>5.053353204172877</v>
       </c>
       <c r="FI9" t="n">
-        <v>122.9016393442623</v>
+        <v>67.49836065573771</v>
       </c>
       <c r="FJ9" t="n">
-        <v>34.7016393442623</v>
+        <v>26.34962742175857</v>
       </c>
       <c r="FK9" t="n">
-        <v>15.42295081967213</v>
+        <v>6.497168405365128</v>
       </c>
       <c r="FL9" t="n">
-        <v>40.9672131147541</v>
+        <v>23.82295081967213</v>
       </c>
       <c r="FM9" t="n">
-        <v>1403.488524590164</v>
+        <v>798.0688524590165</v>
       </c>
       <c r="FN9" t="n">
-        <v>40.48524590163935</v>
+        <v>29.9591654247392</v>
       </c>
       <c r="FO9" t="n">
-        <v>23.61639344262295</v>
+        <v>12.99433681073026</v>
       </c>
       <c r="FP9" t="n">
-        <v>24.58032786885246</v>
+        <v>15.16005961251863</v>
       </c>
       <c r="FQ9" t="n">
-        <v>40.48524590163935</v>
+        <v>53.42116244411328</v>
       </c>
       <c r="FR9" t="n">
-        <v>10.12131147540984</v>
+        <v>3.609538002980627</v>
       </c>
       <c r="FS9" t="n">
-        <v>20.72459016393443</v>
+        <v>12.99433681073026</v>
       </c>
       <c r="FT9" t="n">
-        <v>50.12459016393444</v>
+        <v>35.7344262295082</v>
       </c>
       <c r="FU9" t="n">
-        <v>179.2918032786885</v>
+        <v>131.0262295081967</v>
       </c>
       <c r="FV9" t="n">
-        <v>1122.019672131148</v>
+        <v>580.4137108792847</v>
       </c>
       <c r="FW9" t="n">
-        <v>889.7114754098361</v>
+        <v>421.9549925484353</v>
       </c>
       <c r="FX9" t="n">
-        <v>189.6059016393443</v>
+        <v>129.8350819672131</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.2742622950819673</v>
+        <v>0.2847524424573606</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.6982149362477232</v>
+        <v>0.5501810956058348</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.1818194777424999</v>
+        <v>0.2329011425732737</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.5818047906002289</v>
+        <v>0.6596391636182993</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.08870482630684884</v>
+        <v>0.07076039163426391</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.3985835725404268</v>
+        <v>0.4195534550078862</v>
       </c>
       <c r="GE9" t="n">
-        <v>1.896059016393443</v>
+        <v>1.298350819672131</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.9356897486437414</v>
+        <v>0.6888745191826253</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.1486874817699013</v>
+        <v>0.0801446290402716</v>
       </c>
       <c r="GH9" t="n">
-        <v>1.225759297770924</v>
+        <v>0.6739175340312498</v>
       </c>
       <c r="GI9" t="n">
-        <v>1.215837966836761</v>
+        <v>0.7310927880839382</v>
       </c>
       <c r="GJ9" t="n">
-        <v>0.1216370307660487</v>
+        <v>0.09101064367359664</v>
       </c>
       <c r="GK9" t="n">
-        <v>-1.056929955290611</v>
+        <v>3.859016393442624</v>
       </c>
       <c r="GL9" t="n">
-        <v>-3.392548435171388</v>
+        <v>22.10938897168406</v>
       </c>
       <c r="GM9" t="n">
-        <v>-2.758569299552907</v>
+        <v>8.117138599105813</v>
       </c>
       <c r="GN9" t="n">
-        <v>-13.26795827123698</v>
+        <v>73.38599105812219</v>
       </c>
       <c r="GO9" t="n">
-        <v>-8.554694485842028</v>
+        <v>-5.596125186289122</v>
       </c>
       <c r="GP9" t="n">
-        <v>-4.872429210134131</v>
+        <v>6.274217585692997</v>
       </c>
       <c r="GQ9" t="n">
-        <v>7.656929955290607</v>
+        <v>3.715350223546945</v>
       </c>
       <c r="GR9" t="n">
-        <v>-142.0131147540983</v>
+        <v>770.8160953800299</v>
       </c>
       <c r="GS9" t="n">
-        <v>-8.374962742175867</v>
+        <v>1.171087928464971</v>
       </c>
       <c r="GT9" t="n">
-        <v>-7.102533532041733</v>
+        <v>-0.2229508196721302</v>
       </c>
       <c r="GU9" t="n">
-        <v>13.49329359165425</v>
+        <v>8.387183308494786</v>
       </c>
       <c r="GV9" t="n">
-        <v>20.98301043219075</v>
+        <v>-16.70342771982118</v>
       </c>
       <c r="GW9" t="n">
-        <v>-7.369001490312968</v>
+        <v>0.381520119225037</v>
       </c>
       <c r="GX9" t="n">
-        <v>-0.5409836065573757</v>
+        <v>-5.012220566318928</v>
       </c>
       <c r="GY9" t="n">
-        <v>-6.546348733233991</v>
+        <v>-3.406855439642328</v>
       </c>
       <c r="GZ9" t="n">
-        <v>-12.31833084947843</v>
+        <v>-44.42026825633384</v>
       </c>
       <c r="HA9" t="n">
-        <v>-101.8301043219077</v>
+        <v>765.7701937406857</v>
       </c>
       <c r="HB9" t="n">
-        <v>-93.37645305514161</v>
+        <v>767.7794336810732</v>
       </c>
       <c r="HC9" t="n">
-        <v>-11.34795827123696</v>
+        <v>45.37236959761549</v>
       </c>
       <c r="HD9" t="n">
-        <v>-0.1641095380029807</v>
+        <v>0.04702170738683403</v>
       </c>
       <c r="HE9" t="n">
-        <v>-0.239194817022686</v>
+        <v>0.07499164521519219</v>
       </c>
       <c r="HF9" t="n">
-        <v>-0.07367818798115225</v>
+        <v>-0.08561209282520757</v>
       </c>
       <c r="HG9" t="n">
-        <v>0.1374593252260856</v>
+        <v>0.1116486560301762</v>
       </c>
       <c r="HH9" t="n">
-        <v>0.02113393133958405</v>
+        <v>-0.0314952041266844</v>
       </c>
       <c r="HI9" t="n">
-        <v>-0.01648036795494823</v>
+        <v>-0.2880538762248047</v>
       </c>
       <c r="HJ9" t="n">
-        <v>-0.1134795827123698</v>
+        <v>0.4537236959761548</v>
       </c>
       <c r="HK9" t="n">
-        <v>0.3840641190796008</v>
+        <v>0.480156602817726</v>
       </c>
       <c r="HL9" t="n">
-        <v>-0.04783199478275615</v>
+        <v>0.08140522312974886</v>
       </c>
       <c r="HM9" t="n">
-        <v>-0.1257374764683317</v>
+        <v>0.7337671315673446</v>
       </c>
       <c r="HN9" t="n">
-        <v>-0.1167715683380275</v>
+        <v>0.6142778316288293</v>
       </c>
       <c r="HO9" t="n">
-        <v>0.01160430007374104</v>
+        <v>-0.03312504778217668</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>0</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>4.008941877794337</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>5.189865871833086</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>41.95141579731744</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>13.83964232488823</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>151.8035767511178</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>24.65186289120716</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>16.43457526080477</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>38.49150521609539</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>1705.303427719821</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>31.57168405365127</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>13.40715350223547</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>21.1919523099851</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>34.16661698956781</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>3.459910581222057</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>10.81222056631893</v>
-      </c>
-      <c r="CB10" t="n">
-        <v>36.3290611028316</v>
-      </c>
-      <c r="CC10" t="n">
-        <v>97.74247391952312</v>
-      </c>
-      <c r="CD10" t="n">
-        <v>1469.164530551416</v>
-      </c>
-      <c r="CE10" t="n">
-        <v>1295.304023845008</v>
-      </c>
-      <c r="CF10" t="n">
-        <v>189.4301043219076</v>
-      </c>
-      <c r="CG10" t="n">
-        <v>0.2874437658714857</v>
-      </c>
-      <c r="CH10" t="n">
-        <v>0.6594446413000811</v>
-      </c>
-      <c r="CI10" t="n">
-        <v>0.3449613228301753</v>
-      </c>
-      <c r="CJ10" t="n">
-        <v>0.8049097532704091</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>0.05403153778659991</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>0.1468094298254771</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>1.894301043219077</v>
-      </c>
-      <c r="CN10" t="n">
-        <v>1.197505052149569</v>
-      </c>
-      <c r="CO10" t="n">
-        <v>0.1624006203727799</v>
-      </c>
-      <c r="CP10" t="n">
-        <v>1.515142385961502</v>
-      </c>
-      <c r="CQ10" t="n">
-        <v>1.44197105636125</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>0.07760923988318315</v>
-      </c>
-      <c r="CS10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CY10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DC10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DH10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DN10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DW10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DX10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DY10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="EA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC10" t="n">
-        <v>1</v>
-      </c>
-      <c r="ED10" t="n">
-        <v>1</v>
-      </c>
-      <c r="EE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF10" t="n">
-        <v>1</v>
-      </c>
-      <c r="EG10" t="n">
-        <v>1</v>
-      </c>
-      <c r="EH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="EI10" t="n">
-        <v>1</v>
-      </c>
-      <c r="EJ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="EK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="EL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="EM10" t="n">
-        <v>1</v>
-      </c>
-      <c r="EN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="EO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="EP10" t="n">
-        <v>1</v>
-      </c>
-      <c r="EQ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="ER10" t="n">
-        <v>1</v>
-      </c>
-      <c r="ES10" t="n">
-        <v>1</v>
-      </c>
-      <c r="ET10" t="n">
-        <v>0</v>
-      </c>
-      <c r="EU10" t="n">
-        <v>1</v>
-      </c>
-      <c r="EV10" t="n">
-        <v>1</v>
-      </c>
-      <c r="EW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="EX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="EY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="EZ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="FA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="FB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="FC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="FD10" t="n">
-        <v>1</v>
-      </c>
-      <c r="FE10" t="n">
-        <v>2.026825633383011</v>
-      </c>
-      <c r="FF10" t="n">
-        <v>2.214605067064084</v>
-      </c>
-      <c r="FG10" t="n">
-        <v>19.48852459016394</v>
-      </c>
-      <c r="FH10" t="n">
-        <v>4.872131147540984</v>
-      </c>
-      <c r="FI10" t="n">
-        <v>116.9311475409836</v>
-      </c>
-      <c r="FJ10" t="n">
-        <v>25.68941877794337</v>
-      </c>
-      <c r="FK10" t="n">
-        <v>11.95886736214605</v>
-      </c>
-      <c r="FL10" t="n">
-        <v>35.43368107302534</v>
-      </c>
-      <c r="FM10" t="n">
-        <v>1314.58956780924</v>
-      </c>
-      <c r="FN10" t="n">
-        <v>34.10491803278689</v>
-      </c>
-      <c r="FO10" t="n">
-        <v>12.84470938897169</v>
-      </c>
-      <c r="FP10" t="n">
-        <v>20.37436661698957</v>
-      </c>
-      <c r="FQ10" t="n">
-        <v>53.59344262295082</v>
-      </c>
-      <c r="FR10" t="n">
-        <v>2.657526080476901</v>
-      </c>
-      <c r="FS10" t="n">
-        <v>19.04560357675112</v>
-      </c>
-      <c r="FT10" t="n">
-        <v>44.73502235469449</v>
-      </c>
-      <c r="FU10" t="n">
-        <v>135.9767511177348</v>
-      </c>
-      <c r="FV10" t="n">
-        <v>1092.686140089419</v>
-      </c>
-      <c r="FW10" t="n">
-        <v>885.3991058122207</v>
-      </c>
-      <c r="FX10" t="n">
-        <v>179.0729657228018</v>
-      </c>
-      <c r="FY10" t="n">
-        <v>0.2636434603647719</v>
-      </c>
-      <c r="FZ10" t="n">
-        <v>0.6591086509119297</v>
-      </c>
-      <c r="GA10" t="n">
-        <v>0.1376827271089566</v>
-      </c>
-      <c r="GB10" t="n">
-        <v>0.5569256079241176</v>
-      </c>
-      <c r="GC10" t="n">
-        <v>0.07516815316516041</v>
-      </c>
-      <c r="GD10" t="n">
-        <v>0.2808708101858756</v>
-      </c>
-      <c r="GE10" t="n">
-        <v>1.790729657228018</v>
-      </c>
-      <c r="GF10" t="n">
-        <v>1.25679439818337</v>
-      </c>
-      <c r="GG10" t="n">
-        <v>0.1050006632178616</v>
-      </c>
-      <c r="GH10" t="n">
-        <v>1.167947736715107</v>
-      </c>
-      <c r="GI10" t="n">
-        <v>1.144155904691089</v>
-      </c>
-      <c r="GJ10" t="n">
-        <v>0.1006236157909935</v>
-      </c>
-      <c r="GK10" t="n">
-        <v>2.975260804769002</v>
-      </c>
-      <c r="GL10" t="n">
-        <v>22.4628912071535</v>
-      </c>
-      <c r="GM10" t="n">
-        <v>8.967511177347244</v>
-      </c>
-      <c r="GN10" t="n">
-        <v>34.87242921013414</v>
-      </c>
-      <c r="GO10" t="n">
-        <v>-1.037555886736211</v>
-      </c>
-      <c r="GP10" t="n">
-        <v>4.475707898658717</v>
-      </c>
-      <c r="GQ10" t="n">
-        <v>3.05782414307005</v>
-      </c>
-      <c r="GR10" t="n">
-        <v>390.7138599105813</v>
-      </c>
-      <c r="GS10" t="n">
-        <v>-2.53323397913562</v>
-      </c>
-      <c r="GT10" t="n">
-        <v>0.562444113263787</v>
-      </c>
-      <c r="GU10" t="n">
-        <v>0.8175856929955323</v>
-      </c>
-      <c r="GV10" t="n">
-        <v>-19.42682563338301</v>
-      </c>
-      <c r="GW10" t="n">
-        <v>0.8023845007451569</v>
-      </c>
-      <c r="GX10" t="n">
-        <v>-8.233383010432192</v>
-      </c>
-      <c r="GY10" t="n">
-        <v>-8.405961251862891</v>
-      </c>
-      <c r="GZ10" t="n">
-        <v>-38.23427719821163</v>
-      </c>
-      <c r="HA10" t="n">
-        <v>376.4783904619972</v>
-      </c>
-      <c r="HB10" t="n">
-        <v>409.9049180327869</v>
-      </c>
-      <c r="HC10" t="n">
-        <v>10.35713859910584</v>
-      </c>
-      <c r="HD10" t="n">
-        <v>0.02380030550671386</v>
-      </c>
-      <c r="HE10" t="n">
-        <v>0.0003359903881513526</v>
-      </c>
-      <c r="HF10" t="n">
-        <v>0.2072785957212187</v>
-      </c>
-      <c r="HG10" t="n">
-        <v>0.2479841453462915</v>
-      </c>
-      <c r="HH10" t="n">
-        <v>-0.02113661537856051</v>
-      </c>
-      <c r="HI10" t="n">
-        <v>-0.1340613803603985</v>
-      </c>
-      <c r="HJ10" t="n">
-        <v>0.1035713859910585</v>
-      </c>
-      <c r="HK10" t="n">
-        <v>-0.05928934603380132</v>
-      </c>
-      <c r="HL10" t="n">
-        <v>0.0573999571549183</v>
-      </c>
-      <c r="HM10" t="n">
-        <v>0.3471946492463951</v>
-      </c>
-      <c r="HN10" t="n">
-        <v>0.2978151516701604</v>
-      </c>
-      <c r="HO10" t="n">
-        <v>-0.0230143759078104</v>
-      </c>
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr"/>
+      <c r="BW10" t="inlineStr"/>
+      <c r="BX10" t="inlineStr"/>
+      <c r="BY10" t="inlineStr"/>
+      <c r="BZ10" t="inlineStr"/>
+      <c r="CA10" t="inlineStr"/>
+      <c r="CB10" t="inlineStr"/>
+      <c r="CC10" t="inlineStr"/>
+      <c r="CD10" t="inlineStr"/>
+      <c r="CE10" t="inlineStr"/>
+      <c r="CF10" t="inlineStr"/>
+      <c r="CG10" t="inlineStr"/>
+      <c r="CH10" t="inlineStr"/>
+      <c r="CI10" t="inlineStr"/>
+      <c r="CJ10" t="inlineStr"/>
+      <c r="CK10" t="inlineStr"/>
+      <c r="CL10" t="inlineStr"/>
+      <c r="CM10" t="inlineStr"/>
+      <c r="CN10" t="inlineStr"/>
+      <c r="CO10" t="inlineStr"/>
+      <c r="CP10" t="inlineStr"/>
+      <c r="CQ10" t="inlineStr"/>
+      <c r="CR10" t="inlineStr"/>
+      <c r="CS10" t="inlineStr"/>
+      <c r="CT10" t="inlineStr"/>
+      <c r="CU10" t="inlineStr"/>
+      <c r="CV10" t="inlineStr"/>
+      <c r="CW10" t="inlineStr"/>
+      <c r="CX10" t="inlineStr"/>
+      <c r="CY10" t="inlineStr"/>
+      <c r="CZ10" t="inlineStr"/>
+      <c r="DA10" t="inlineStr"/>
+      <c r="DB10" t="inlineStr"/>
+      <c r="DC10" t="inlineStr"/>
+      <c r="DD10" t="inlineStr"/>
+      <c r="DE10" t="inlineStr"/>
+      <c r="DF10" t="inlineStr"/>
+      <c r="DG10" t="inlineStr"/>
+      <c r="DH10" t="inlineStr"/>
+      <c r="DI10" t="inlineStr"/>
+      <c r="DJ10" t="inlineStr"/>
+      <c r="DK10" t="inlineStr"/>
+      <c r="DL10" t="inlineStr"/>
+      <c r="DM10" t="inlineStr"/>
+      <c r="DN10" t="inlineStr"/>
+      <c r="DO10" t="inlineStr"/>
+      <c r="DP10" t="inlineStr"/>
+      <c r="DQ10" t="inlineStr"/>
+      <c r="DR10" t="inlineStr"/>
+      <c r="DS10" t="inlineStr"/>
+      <c r="DT10" t="inlineStr"/>
+      <c r="DU10" t="inlineStr"/>
+      <c r="DV10" t="inlineStr"/>
+      <c r="DW10" t="inlineStr"/>
+      <c r="DX10" t="inlineStr"/>
+      <c r="DY10" t="inlineStr"/>
+      <c r="DZ10" t="inlineStr"/>
+      <c r="EA10" t="inlineStr"/>
+      <c r="EB10" t="inlineStr"/>
+      <c r="EC10" t="inlineStr"/>
+      <c r="ED10" t="inlineStr"/>
+      <c r="EE10" t="inlineStr"/>
+      <c r="EF10" t="inlineStr"/>
+      <c r="EG10" t="inlineStr"/>
+      <c r="EH10" t="inlineStr"/>
+      <c r="EI10" t="inlineStr"/>
+      <c r="EJ10" t="inlineStr"/>
+      <c r="EK10" t="inlineStr"/>
+      <c r="EL10" t="inlineStr"/>
+      <c r="EM10" t="inlineStr"/>
+      <c r="EN10" t="inlineStr"/>
+      <c r="EO10" t="inlineStr"/>
+      <c r="EP10" t="inlineStr"/>
+      <c r="EQ10" t="inlineStr"/>
+      <c r="ER10" t="inlineStr"/>
+      <c r="ES10" t="inlineStr"/>
+      <c r="ET10" t="inlineStr"/>
+      <c r="EU10" t="inlineStr"/>
+      <c r="EV10" t="inlineStr"/>
+      <c r="EW10" t="inlineStr"/>
+      <c r="EX10" t="inlineStr"/>
+      <c r="EY10" t="inlineStr"/>
+      <c r="EZ10" t="inlineStr"/>
+      <c r="FA10" t="inlineStr"/>
+      <c r="FB10" t="inlineStr"/>
+      <c r="FC10" t="inlineStr"/>
+      <c r="FD10" t="inlineStr"/>
+      <c r="FE10" t="inlineStr"/>
+      <c r="FF10" t="inlineStr"/>
+      <c r="FG10" t="inlineStr"/>
+      <c r="FH10" t="inlineStr"/>
+      <c r="FI10" t="inlineStr"/>
+      <c r="FJ10" t="inlineStr"/>
+      <c r="FK10" t="inlineStr"/>
+      <c r="FL10" t="inlineStr"/>
+      <c r="FM10" t="inlineStr"/>
+      <c r="FN10" t="inlineStr"/>
+      <c r="FO10" t="inlineStr"/>
+      <c r="FP10" t="inlineStr"/>
+      <c r="FQ10" t="inlineStr"/>
+      <c r="FR10" t="inlineStr"/>
+      <c r="FS10" t="inlineStr"/>
+      <c r="FT10" t="inlineStr"/>
+      <c r="FU10" t="inlineStr"/>
+      <c r="FV10" t="inlineStr"/>
+      <c r="FW10" t="inlineStr"/>
+      <c r="FX10" t="inlineStr"/>
+      <c r="FY10" t="inlineStr"/>
+      <c r="FZ10" t="inlineStr"/>
+      <c r="GA10" t="inlineStr"/>
+      <c r="GB10" t="inlineStr"/>
+      <c r="GC10" t="inlineStr"/>
+      <c r="GD10" t="inlineStr"/>
+      <c r="GE10" t="inlineStr"/>
+      <c r="GF10" t="inlineStr"/>
+      <c r="GG10" t="inlineStr"/>
+      <c r="GH10" t="inlineStr"/>
+      <c r="GI10" t="inlineStr"/>
+      <c r="GJ10" t="inlineStr"/>
+      <c r="GK10" t="inlineStr"/>
+      <c r="GL10" t="inlineStr"/>
+      <c r="GM10" t="inlineStr"/>
+      <c r="GN10" t="inlineStr"/>
+      <c r="GO10" t="inlineStr"/>
+      <c r="GP10" t="inlineStr"/>
+      <c r="GQ10" t="inlineStr"/>
+      <c r="GR10" t="inlineStr"/>
+      <c r="GS10" t="inlineStr"/>
+      <c r="GT10" t="inlineStr"/>
+      <c r="GU10" t="inlineStr"/>
+      <c r="GV10" t="inlineStr"/>
+      <c r="GW10" t="inlineStr"/>
+      <c r="GX10" t="inlineStr"/>
+      <c r="GY10" t="inlineStr"/>
+      <c r="GZ10" t="inlineStr"/>
+      <c r="HA10" t="inlineStr"/>
+      <c r="HB10" t="inlineStr"/>
+      <c r="HC10" t="inlineStr"/>
+      <c r="HD10" t="inlineStr"/>
+      <c r="HE10" t="inlineStr"/>
+      <c r="HF10" t="inlineStr"/>
+      <c r="HG10" t="inlineStr"/>
+      <c r="HH10" t="inlineStr"/>
+      <c r="HI10" t="inlineStr"/>
+      <c r="HJ10" t="inlineStr"/>
+      <c r="HK10" t="inlineStr"/>
+      <c r="HL10" t="inlineStr"/>
+      <c r="HM10" t="inlineStr"/>
+      <c r="HN10" t="inlineStr"/>
+      <c r="HO10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7146,7 +7146,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -7158,19 +7158,19 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -7185,16 +7185,16 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -7221,7 +7221,7 @@
         <v>1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -7239,19 +7239,19 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM11" t="n">
         <v>1</v>
@@ -7260,7 +7260,7 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
@@ -7269,22 +7269,22 @@
         <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV11" t="n">
         <v>1</v>
       </c>
       <c r="AW11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
         <v>1</v>
@@ -7296,13 +7296,13 @@
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
         <v>1</v>
@@ -7311,139 +7311,139 @@
         <v>1</v>
       </c>
       <c r="BF11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>1</v>
       </c>
       <c r="BH11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
         <v>1</v>
       </c>
       <c r="BK11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.84053651266766</v>
+        <v>2.86140089418778</v>
       </c>
       <c r="BN11" t="n">
-        <v>2.891803278688525</v>
+        <v>4.614008941877795</v>
       </c>
       <c r="BO11" t="n">
-        <v>22.72131147540984</v>
+        <v>27.68405365126677</v>
       </c>
       <c r="BP11" t="n">
-        <v>7.849180327868853</v>
+        <v>10.76602086438152</v>
       </c>
       <c r="BQ11" t="n">
-        <v>91.71147540983607</v>
+        <v>95.35618479880776</v>
       </c>
       <c r="BR11" t="n">
-        <v>25.61311475409836</v>
+        <v>18.84053651266766</v>
       </c>
       <c r="BS11" t="n">
-        <v>5.783606557377049</v>
+        <v>11.150521609538</v>
       </c>
       <c r="BT11" t="n">
-        <v>40.8983606557377</v>
+        <v>33.8360655737705</v>
       </c>
       <c r="BU11" t="n">
-        <v>1092.688524590164</v>
+        <v>1228.864381520119</v>
       </c>
       <c r="BV11" t="n">
-        <v>31.80983606557377</v>
+        <v>31.52906110283159</v>
       </c>
       <c r="BW11" t="n">
-        <v>10.74098360655738</v>
+        <v>17.30253353204173</v>
       </c>
       <c r="BX11" t="n">
-        <v>30.57049180327869</v>
+        <v>16.91803278688525</v>
       </c>
       <c r="BY11" t="n">
-        <v>54.94426229508197</v>
+        <v>29.60655737704918</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.478688524590164</v>
+        <v>1.153502235469449</v>
       </c>
       <c r="CA11" t="n">
-        <v>15.28524590163935</v>
+        <v>14.22652757078987</v>
       </c>
       <c r="CB11" t="n">
-        <v>36.7672131147541</v>
+        <v>33.06706408345753</v>
       </c>
       <c r="CC11" t="n">
-        <v>131.3704918032787</v>
+        <v>93.43368107302534</v>
       </c>
       <c r="CD11" t="n">
-        <v>872.4983606557377</v>
+        <v>1034.307004470939</v>
       </c>
       <c r="CE11" t="n">
-        <v>673.7901639344262</v>
+        <v>892.8107302533532</v>
       </c>
       <c r="CF11" t="n">
-        <v>158.6773770491803</v>
+        <v>164.8354694485842</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.314703656998739</v>
+        <v>0.308173974429367</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.7312610340479193</v>
+        <v>0.7120009412502942</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.1342622950819672</v>
+        <v>0.1798106425878847</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.6695901639344263</v>
+        <v>0.79896993074428</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.09462095374573</v>
+        <v>0.0618041042715031</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.3155314120768661</v>
+        <v>0.1818915202082098</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.586773770491803</v>
+        <v>1.648354694485842</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.9389337477004156</v>
+        <v>1.18072565915534</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.08250722446747671</v>
+        <v>0.0906593608804005</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.9173187167280779</v>
+        <v>0.9477891776188083</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.9324894652000211</v>
+        <v>0.9531123745996959</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.1080984217150497</v>
+        <v>0.08188979951191395</v>
       </c>
       <c r="CS11" t="n">
         <v>1</v>
       </c>
       <c r="CT11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CU11" t="n">
         <v>1</v>
       </c>
       <c r="CV11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
         <v>0</v>
       </c>
       <c r="CX11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
@@ -7461,16 +7461,16 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DE11" t="n">
         <v>1</v>
       </c>
       <c r="DF11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DG11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH11" t="n">
         <v>1</v>
@@ -7479,7 +7479,7 @@
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DK11" t="n">
         <v>1</v>
@@ -7491,16 +7491,16 @@
         <v>1</v>
       </c>
       <c r="DN11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DP11" t="n">
         <v>1</v>
       </c>
       <c r="DQ11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
         <v>1</v>
@@ -7509,16 +7509,16 @@
         <v>0</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV11" t="n">
         <v>1</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DX11" t="n">
         <v>0</v>
@@ -7530,52 +7530,52 @@
         <v>0</v>
       </c>
       <c r="EA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EB11" t="n">
         <v>1</v>
       </c>
       <c r="EC11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ED11" t="n">
         <v>1</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EF11" t="n">
         <v>1</v>
       </c>
       <c r="EG11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EI11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EJ11" t="n">
         <v>1</v>
       </c>
       <c r="EK11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EL11" t="n">
         <v>1</v>
       </c>
       <c r="EM11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EN11" t="n">
         <v>0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EP11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EQ11" t="n">
         <v>1</v>
@@ -7587,13 +7587,13 @@
         <v>0</v>
       </c>
       <c r="ET11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EU11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EV11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EW11" t="n">
         <v>1</v>
@@ -7608,205 +7608,205 @@
         <v>1</v>
       </c>
       <c r="FA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FB11" t="n">
         <v>1</v>
       </c>
       <c r="FC11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FD11" t="n">
         <v>1</v>
       </c>
       <c r="FE11" t="n">
-        <v>1.669150521609538</v>
+        <v>2.116244411326379</v>
       </c>
       <c r="FF11" t="n">
-        <v>1.640834575260805</v>
+        <v>1.856333830104322</v>
       </c>
       <c r="FG11" t="n">
-        <v>22.424739195231</v>
+        <v>25.98867362146051</v>
       </c>
       <c r="FH11" t="n">
-        <v>6.016393442622952</v>
+        <v>8.353502235469449</v>
       </c>
       <c r="FI11" t="n">
-        <v>129.0789865871833</v>
+        <v>106.2751117734724</v>
       </c>
       <c r="FJ11" t="n">
-        <v>30.08196721311475</v>
+        <v>27.38092399403875</v>
       </c>
       <c r="FK11" t="n">
-        <v>8.751117734724293</v>
+        <v>8.353502235469449</v>
       </c>
       <c r="FL11" t="n">
-        <v>49.22503725782414</v>
+        <v>39.91117734724292</v>
       </c>
       <c r="FM11" t="n">
-        <v>1503.004470938897</v>
+        <v>1252.097168405365</v>
       </c>
       <c r="FN11" t="n">
-        <v>33.36363636363636</v>
+        <v>31.09359165424739</v>
       </c>
       <c r="FO11" t="n">
-        <v>14.22056631892698</v>
+        <v>19.49150521609538</v>
       </c>
       <c r="FP11" t="n">
-        <v>32.26974664679583</v>
+        <v>38.51892697466469</v>
       </c>
       <c r="FQ11" t="n">
-        <v>67.82116244411327</v>
+        <v>63.57943368107303</v>
       </c>
       <c r="FR11" t="n">
-        <v>4.375558867362146</v>
+        <v>2.320417287630403</v>
       </c>
       <c r="FS11" t="n">
-        <v>25.70640834575261</v>
+        <v>22.74008941877794</v>
       </c>
       <c r="FT11" t="n">
-        <v>49.77198211624441</v>
+        <v>45.0160953800298</v>
       </c>
       <c r="FU11" t="n">
-        <v>197.4470938897169</v>
+        <v>169.8545454545455</v>
       </c>
       <c r="FV11" t="n">
-        <v>1212.029806259314</v>
+        <v>1003.348435171386</v>
       </c>
       <c r="FW11" t="n">
-        <v>947.855439642325</v>
+        <v>781.0524590163935</v>
       </c>
       <c r="FX11" t="n">
-        <v>210.2456035767511</v>
+        <v>179.6002980625932</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.1844853689115984</v>
+        <v>0.1565603184563495</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.7010444018640739</v>
+        <v>0.686762098988156</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.3104716402209169</v>
+        <v>0.1094061001679131</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.9250994353694451</v>
+        <v>0.7001979358508822</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.1066584732701633</v>
+        <v>0.09039512809029324</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.4900794382379746</v>
+        <v>0.4022755004808286</v>
       </c>
       <c r="GE11" t="n">
-        <v>2.102456035767511</v>
+        <v>1.796002980625932</v>
       </c>
       <c r="GF11" t="n">
-        <v>1.190818125213672</v>
+        <v>1.462323559471101</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.1013682650791378</v>
+        <v>0.100367807553642</v>
       </c>
       <c r="GH11" t="n">
-        <v>1.290666145118727</v>
+        <v>1.065953224231351</v>
       </c>
       <c r="GI11" t="n">
-        <v>1.290340232141332</v>
+        <v>1.076852865213887</v>
       </c>
       <c r="GJ11" t="n">
-        <v>0.1283300081299584</v>
+        <v>0.1089416864181627</v>
       </c>
       <c r="GK11" t="n">
-        <v>1.25096870342772</v>
+        <v>2.757675111773472</v>
       </c>
       <c r="GL11" t="n">
-        <v>0.2965722801788395</v>
+        <v>1.695380029806262</v>
       </c>
       <c r="GM11" t="n">
-        <v>1.832786885245901</v>
+        <v>2.412518628912071</v>
       </c>
       <c r="GN11" t="n">
-        <v>-37.36751117734725</v>
+        <v>-10.91892697466467</v>
       </c>
       <c r="GO11" t="n">
-        <v>-4.468852459016393</v>
+        <v>-8.540387481371091</v>
       </c>
       <c r="GP11" t="n">
-        <v>-2.967511177347244</v>
+        <v>2.797019374068554</v>
       </c>
       <c r="GQ11" t="n">
-        <v>-8.326676602086437</v>
+        <v>-6.075111773472422</v>
       </c>
       <c r="GR11" t="n">
-        <v>-410.3159463487332</v>
+        <v>-23.23278688524579</v>
       </c>
       <c r="GS11" t="n">
-        <v>-1.553800298062587</v>
+        <v>0.4354694485842003</v>
       </c>
       <c r="GT11" t="n">
-        <v>-3.479582712369597</v>
+        <v>-2.188971684053655</v>
       </c>
       <c r="GU11" t="n">
-        <v>-1.699254843517139</v>
+        <v>-21.60089418777944</v>
       </c>
       <c r="GV11" t="n">
-        <v>-12.8769001490313</v>
+        <v>-33.97287630402384</v>
       </c>
       <c r="GW11" t="n">
-        <v>-1.896870342771983</v>
+        <v>-1.166915052160954</v>
       </c>
       <c r="GX11" t="n">
-        <v>-10.42116244411326</v>
+        <v>-8.513561847988077</v>
       </c>
       <c r="GY11" t="n">
-        <v>-13.00476900149031</v>
+        <v>-11.94903129657227</v>
       </c>
       <c r="GZ11" t="n">
-        <v>-66.07660208643816</v>
+        <v>-76.42086438152013</v>
       </c>
       <c r="HA11" t="n">
-        <v>-339.5314456035768</v>
+        <v>30.95856929955312</v>
       </c>
       <c r="HB11" t="n">
-        <v>-274.0652757078988</v>
+        <v>111.7582712369597</v>
       </c>
       <c r="HC11" t="n">
-        <v>-51.56822652757077</v>
+        <v>-14.76482861400896</v>
       </c>
       <c r="HD11" t="n">
-        <v>0.1302182880871406</v>
+        <v>0.1516136559730175</v>
       </c>
       <c r="HE11" t="n">
-        <v>0.0302166321838454</v>
+        <v>0.02523884226213824</v>
       </c>
       <c r="HF11" t="n">
-        <v>-0.1762093451389498</v>
+        <v>0.07040454241997154</v>
       </c>
       <c r="HG11" t="n">
-        <v>-0.2555092714350188</v>
+        <v>0.09877199489339783</v>
       </c>
       <c r="HH11" t="n">
-        <v>-0.01203751952443328</v>
+        <v>-0.02859102381879014</v>
       </c>
       <c r="HI11" t="n">
-        <v>-0.1745480261611085</v>
+        <v>-0.2203839802726188</v>
       </c>
       <c r="HJ11" t="n">
-        <v>-0.5156822652757076</v>
+        <v>-0.1476482861400898</v>
       </c>
       <c r="HK11" t="n">
-        <v>-0.251884377513256</v>
+        <v>-0.2815979003157609</v>
       </c>
       <c r="HL11" t="n">
-        <v>-0.01886104061166106</v>
+        <v>-0.009708446673241541</v>
       </c>
       <c r="HM11" t="n">
-        <v>-0.373347428390649</v>
+        <v>-0.1181640466125429</v>
       </c>
       <c r="HN11" t="n">
-        <v>-0.3578507669413107</v>
+        <v>-0.123740490614191</v>
       </c>
       <c r="HO11" t="n">
-        <v>-0.02023158641490874</v>
+        <v>-0.02705188690624874</v>
       </c>
     </row>
   </sheetData>
